--- a/wwwroot/ExcelModel/Tchibo_WET_sheet.xlsx
+++ b/wwwroot/ExcelModel/Tchibo_WET_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB2ADD-D703-4105-850F-F0444CB0C606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC93E5D3-7816-4BA0-BDC3-8B7CDECC1A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="768" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="768" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppearanceAfterWashing" sheetId="25" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="229">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -146,43 +146,43 @@
   </si>
   <si>
     <t>Original</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Average</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>(cm)</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>(%)</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Weft1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Weft2</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Weft3</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Warp1</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Warp2</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Warp3</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -199,11 +199,11 @@
       </rPr>
       <t>报告编号:</t>
     </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Cross staining</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Lengthwise经向(%)</t>
@@ -319,49 +319,49 @@
   </si>
   <si>
     <t xml:space="preserve">           width            宽)</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>1g/l  Sodium  perborate  solution and</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">% available chlorine with </t>
   </si>
   <si>
     <t>steel balls.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                   Cotton</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                   Polyamide(Nylon)</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                   Polyester</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                   Acrylic</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                   Wool</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">℃ with 4g/l ‘ECE(B)’ detergent and  </t>
   </si>
   <si>
     <t xml:space="preserve">Test No.: </t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Dimensional Stability to Washing/ Dry-cleaning尺寸稳定性-水洗/干洗</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Procedure No: </t>
@@ -509,23 +509,23 @@
   </si>
   <si>
     <t>Appearance After Washing 水洗后外观-Fabric&amp;Components</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Remark 备注（+）Means Extension 伸长</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>（-）Means Shrinkage</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Original</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>.Seam twisting</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -551,7 +551,7 @@
       </rPr>
       <t>（cm/inch）长</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -577,7 +577,7 @@
       </rPr>
       <t>（cm/inch）宽</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -603,23 +603,23 @@
       </rPr>
       <t>（%）</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Remark:     </t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Skews &amp; Spirality(%) = S/L ×100</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>L = Lengthwise dimension</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>S = Skewness dimension</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -771,7 +771,7 @@
   </si>
   <si>
     <t>10.(   ) Trademark: Negligible change</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -818,35 +818,35 @@
   </si>
   <si>
     <t>Observation on washed sample After</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Dry Pressing</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Immediately:</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Change in shade</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Staining on cotton</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>After 4 hours:</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Miele: Machine wash at:</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>, with 4.0kg total dry ballast,</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -929,23 +929,23 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>°C</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>°C ×</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>hours.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                neck opening(领围)</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -990,31 +990,31 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>After</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Wash</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Sample</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Staining on </t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Polyester</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Colour Fastness to Water 耐水色牢度</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1040,22 +1040,22 @@
       </rPr>
       <t>耐唾液和汗渍色牢度</t>
     </r>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Saliva Staining on filter paper</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Sweat Staining on filter paper</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>light (when ≥4-5)</t>
   </si>
   <si>
     <t xml:space="preserve">Fluorescence under UV </t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                          Fluorescence assessment is only needed when the result is no less than 4-5.</t>
@@ -1065,15 +1065,15 @@
   </si>
   <si>
     <t xml:space="preserve"> where 1 is bad and 5 is good. </t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Remarks: Grey Scale Rating is based on the 5-step scale of 1 to 5,</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Sample样品</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1098,7 +1098,7 @@
       </rPr>
       <t>:</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1120,7 +1120,7 @@
       </rPr>
       <t xml:space="preserve"> Resist to sweat &amp; saliva</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1166,27 +1166,27 @@
   </si>
   <si>
     <t>Hot Pressing Temperature:</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Colour Fastness to Hot Pressing 耐热压色牢度</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Colour Fastness to Sublimation in Storage 耐升华色牢度</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>Damp Pressing</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Wet Pressing</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>/</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1204,15 +1204,15 @@
       </rPr>
       <t>耐氯水色牢度</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Change in Shade</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">°C with </t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>machine,</t>
@@ -1257,58 +1257,58 @@
       </rPr>
       <t>3%;)</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>(cotton&lt;=±5%, synthetics &lt;=±3%;)</t>
   </si>
   <si>
     <t xml:space="preserve">After </t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Concentration：</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>mg/L</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Temperature：</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Dimensional Stability to Washing 尺寸稳定性-水洗</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> ,with 4.0kg total dry ballast,</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>General Apperance 外观</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>，</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Iron.</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>,</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Saliva</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Sweat</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">,using domestic washing </t>
@@ -1318,27 +1318,34 @@
   </si>
   <si>
     <t>wash,</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>iron</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
   <si>
     <t>Dyed 交叉</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cycle</t>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="50">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1716,6 +1723,37 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1931,23 +1969,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1963,385 +2001,385 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2377,7 +2415,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2386,16 +2424,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2407,16 +2445,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2425,10 +2457,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2449,40 +2487,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2491,22 +2529,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2518,29 +2565,23 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2819,98 +2860,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55BC63F-831C-4364-AA36-AED25C27B542}">
   <dimension ref="A1:CA54"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="3" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="1.6640625" style="34" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.88671875" style="34" hidden="1" customWidth="1"/>
-    <col min="8" max="13" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.44140625" style="34" hidden="1" customWidth="1"/>
-    <col min="15" max="42" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="2.33203125" style="34" hidden="1" customWidth="1"/>
-    <col min="44" max="115" width="2.33203125" style="34" customWidth="1"/>
-    <col min="116" max="16384" width="8.88671875" style="34"/>
+    <col min="1" max="3" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="1.640625" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" style="33" hidden="1" customWidth="1"/>
+    <col min="8" max="13" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="33" hidden="1" customWidth="1"/>
+    <col min="15" max="42" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="2.35546875" style="33" hidden="1" customWidth="1"/>
+    <col min="44" max="58" width="2.35546875" style="33" customWidth="1"/>
+    <col min="59" max="59" width="2.85546875" style="33" customWidth="1"/>
+    <col min="60" max="115" width="2.35546875" style="33" customWidth="1"/>
+    <col min="116" max="16384" width="8.85546875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:79">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="AR1" s="34" t="s">
+      <c r="AR1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="BC1" s="112"/>
-      <c r="BD1" s="112"/>
-      <c r="BE1" s="112"/>
-      <c r="BF1" s="112"/>
-      <c r="BG1" s="112"/>
-      <c r="BH1" s="112"/>
-      <c r="BI1" s="112"/>
-      <c r="BJ1" s="112"/>
-      <c r="BK1" s="112"/>
-      <c r="BL1" s="112"/>
-      <c r="BM1" s="112"/>
-      <c r="BN1" s="112"/>
-      <c r="BO1" s="112"/>
-      <c r="BP1" s="112"/>
-      <c r="BQ1" s="112"/>
-      <c r="BR1" s="112"/>
-      <c r="BS1" s="112"/>
-      <c r="BT1" s="112"/>
-      <c r="BU1" s="112"/>
-      <c r="BV1" s="112"/>
-      <c r="BW1" s="112"/>
-      <c r="BX1" s="112"/>
-      <c r="BY1" s="112"/>
-      <c r="BZ1" s="112"/>
-      <c r="CA1" s="112"/>
+      <c r="BC1" s="113"/>
+      <c r="BD1" s="113"/>
+      <c r="BE1" s="113"/>
+      <c r="BF1" s="113"/>
+      <c r="BG1" s="113"/>
+      <c r="BH1" s="113"/>
+      <c r="BI1" s="113"/>
+      <c r="BJ1" s="113"/>
+      <c r="BK1" s="113"/>
+      <c r="BL1" s="113"/>
+      <c r="BM1" s="113"/>
+      <c r="BN1" s="113"/>
+      <c r="BO1" s="113"/>
+      <c r="BP1" s="113"/>
+      <c r="BQ1" s="113"/>
+      <c r="BR1" s="113"/>
+      <c r="BS1" s="113"/>
+      <c r="BT1" s="113"/>
+      <c r="BU1" s="113"/>
+      <c r="BV1" s="113"/>
+      <c r="BW1" s="113"/>
+      <c r="BX1" s="113"/>
+      <c r="BY1" s="113"/>
+      <c r="BZ1" s="113"/>
+      <c r="CA1" s="113"/>
     </row>
     <row r="2" spans="1:79">
-      <c r="AR2" s="35" t="s">
+      <c r="AR2" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
+      <c r="AS2" s="34"/>
+      <c r="AT2" s="34"/>
+      <c r="AU2" s="34"/>
+      <c r="AV2" s="34"/>
+      <c r="AW2" s="34"/>
+      <c r="AX2" s="34"/>
+      <c r="AY2" s="34"/>
+      <c r="AZ2" s="34"/>
+      <c r="BA2" s="34"/>
+      <c r="BB2" s="34"/>
+      <c r="BC2" s="34"/>
+      <c r="BD2" s="34"/>
+      <c r="BE2" s="34"/>
+      <c r="BF2" s="34"/>
+      <c r="BG2" s="34"/>
+      <c r="BH2" s="34"/>
+      <c r="BI2" s="34"/>
+      <c r="BJ2" s="34"/>
+      <c r="BK2" s="34"/>
+      <c r="BL2" s="34"/>
+      <c r="BM2" s="34"/>
+      <c r="BN2" s="34"/>
+      <c r="BO2" s="34"/>
+      <c r="BP2" s="34"/>
+      <c r="BQ2" s="34"/>
+      <c r="BR2" s="34"/>
+      <c r="BS2" s="34"/>
+      <c r="BT2" s="34"/>
+      <c r="BU2" s="34"/>
+      <c r="BV2" s="34"/>
+      <c r="BW2" s="34"/>
+      <c r="BX2" s="34"/>
+      <c r="BY2" s="34"/>
+      <c r="BZ2" s="34"/>
+      <c r="CA2" s="34"/>
     </row>
     <row r="3" spans="1:79">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="AR3" s="35" t="s">
+      <c r="AR3" s="34" t="s">
         <v>218</v>
       </c>
     </row>
@@ -2945,31 +2988,31 @@
       <c r="BJ4" s="94"/>
     </row>
     <row r="5" spans="1:79">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>82</v>
       </c>
       <c r="H5" s="100"/>
       <c r="I5" s="100"/>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="AE5" s="34" t="s">
+      <c r="AE5" s="33" t="s">
         <v>84</v>
       </c>
       <c r="AM5" s="101"/>
       <c r="AN5" s="101"/>
-      <c r="AO5" s="36"/>
-      <c r="AR5" s="113" t="s">
+      <c r="AO5" s="35"/>
+      <c r="AR5" s="114" t="s">
         <v>134</v>
       </c>
-      <c r="AS5" s="113"/>
-      <c r="AT5" s="113"/>
-      <c r="AU5" s="113"/>
-      <c r="AV5" s="113"/>
-      <c r="AW5" s="113"/>
-      <c r="AX5" s="113"/>
-      <c r="AY5" s="113"/>
-      <c r="AZ5" s="113"/>
+      <c r="AS5" s="114"/>
+      <c r="AT5" s="114"/>
+      <c r="AU5" s="114"/>
+      <c r="AV5" s="114"/>
+      <c r="AW5" s="114"/>
+      <c r="AX5" s="114"/>
+      <c r="AY5" s="114"/>
+      <c r="AZ5" s="114"/>
       <c r="BA5" s="99"/>
       <c r="BB5" s="99"/>
       <c r="BC5" s="99"/>
@@ -2999,10 +3042,10 @@
       <c r="CA5" s="99"/>
     </row>
     <row r="6" spans="1:79">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="Q6" s="34" t="s">
+      <c r="Q6" s="33" t="s">
         <v>86</v>
       </c>
       <c r="R6" s="100"/>
@@ -3016,24 +3059,24 @@
       <c r="Z6" s="100"/>
       <c r="AA6" s="100"/>
       <c r="AB6" s="100"/>
-      <c r="AC6" s="34" t="s">
+      <c r="AC6" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="AD6" s="34" t="s">
+      <c r="AD6" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="AI6" s="34" t="s">
+      <c r="AI6" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="AR6" s="113"/>
-      <c r="AS6" s="113"/>
-      <c r="AT6" s="113"/>
-      <c r="AU6" s="113"/>
-      <c r="AV6" s="113"/>
-      <c r="AW6" s="113"/>
-      <c r="AX6" s="113"/>
-      <c r="AY6" s="113"/>
-      <c r="AZ6" s="113"/>
+      <c r="AR6" s="114"/>
+      <c r="AS6" s="114"/>
+      <c r="AT6" s="114"/>
+      <c r="AU6" s="114"/>
+      <c r="AV6" s="114"/>
+      <c r="AW6" s="114"/>
+      <c r="AX6" s="114"/>
+      <c r="AY6" s="114"/>
+      <c r="AZ6" s="114"/>
       <c r="BA6" s="97" t="s">
         <v>133</v>
       </c>
@@ -3044,7 +3087,7 @@
         <v>179</v>
       </c>
       <c r="BF6" s="95"/>
-      <c r="BG6" s="87"/>
+      <c r="BG6" s="90"/>
       <c r="BH6" s="95" t="s">
         <v>180</v>
       </c>
@@ -3059,7 +3102,7 @@
         <v>179</v>
       </c>
       <c r="BO6" s="95"/>
-      <c r="BP6" s="87"/>
+      <c r="BP6" s="85"/>
       <c r="BQ6" s="95" t="s">
         <v>180</v>
       </c>
@@ -3074,24 +3117,24 @@
         <v>179</v>
       </c>
       <c r="BX6" s="95"/>
-      <c r="BY6" s="87"/>
+      <c r="BY6" s="85"/>
       <c r="BZ6" s="95" t="s">
         <v>180</v>
       </c>
       <c r="CA6" s="96"/>
     </row>
     <row r="7" spans="1:79">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="33" t="s">
         <v>90</v>
       </c>
       <c r="N7" s="100"/>
       <c r="O7" s="100"/>
       <c r="P7" s="100"/>
       <c r="Q7" s="100"/>
-      <c r="R7" s="36" t="s">
+      <c r="R7" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="S7" s="34" t="s">
+      <c r="S7" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AR7" s="98" t="s">
@@ -3134,11 +3177,11 @@
       <c r="CA7" s="98"/>
     </row>
     <row r="8" spans="1:79">
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="35"/>
       <c r="AR8" s="98" t="s">
         <v>136</v>
       </c>
@@ -3228,58 +3271,58 @@
       <c r="CA9" s="98"/>
     </row>
     <row r="10" spans="1:79">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="39" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="102"/>
       <c r="I10" s="102"/>
       <c r="K10" s="101"/>
       <c r="L10" s="101"/>
-      <c r="M10" s="39" t="s">
+      <c r="M10" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="O10" s="40" t="s">
+      <c r="O10" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="P10" s="34" t="s">
+      <c r="P10" s="33" t="s">
         <v>84</v>
       </c>
       <c r="X10" s="100"/>
       <c r="Y10" s="100"/>
-      <c r="Z10" s="34" t="s">
+      <c r="Z10" s="33" t="s">
         <v>94</v>
       </c>
       <c r="AI10" s="100"/>
       <c r="AJ10" s="100"/>
-      <c r="AK10" s="34" t="s">
+      <c r="AK10" s="33" t="s">
         <v>95</v>
       </c>
       <c r="AN10" s="100"/>
       <c r="AO10" s="100"/>
       <c r="AP10" s="100"/>
-      <c r="AR10" s="34" t="s">
+      <c r="AR10" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="AW10" s="34" t="s">
+      <c r="AW10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="BJ10" s="34" t="s">
+      <c r="BJ10" s="33" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:79">
       <c r="A11" s="100"/>
       <c r="B11" s="100"/>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AW11" s="34" t="s">
+      <c r="AW11" s="33" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3294,13 +3337,13 @@
       <c r="H12" s="100"/>
       <c r="I12" s="100"/>
     </row>
-    <row r="13" spans="1:79" ht="14.4">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:79">
+      <c r="A13" s="33" t="s">
         <v>96</v>
       </c>
       <c r="G13" s="102"/>
       <c r="H13" s="102"/>
-      <c r="I13" s="34" t="s">
+      <c r="I13" s="33" t="s">
         <v>97</v>
       </c>
       <c r="K13" s="100"/>
@@ -3308,36 +3351,34 @@
       <c r="M13" s="100"/>
       <c r="N13" s="100"/>
       <c r="O13" s="100"/>
-      <c r="P13" s="34" t="s">
+      <c r="P13" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AR13" s="53" t="s">
+      <c r="AR13" s="52" t="s">
         <v>165</v>
       </c>
       <c r="BE13" s="112"/>
       <c r="BF13" s="112"/>
-      <c r="BG13" s="53" t="s">
+      <c r="BG13" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="BI13" s="112"/>
-      <c r="BJ13" s="112"/>
-      <c r="BK13" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="BL13" s="90"/>
-      <c r="BM13" s="112"/>
-      <c r="BN13" s="112"/>
-      <c r="BO13" s="112"/>
-      <c r="BP13" s="112"/>
-      <c r="BQ13" s="112"/>
-      <c r="BR13" s="112"/>
-      <c r="BS13" s="112"/>
-      <c r="BT13" s="112"/>
-      <c r="BU13" s="65" t="s">
+      <c r="BI13" s="113"/>
+      <c r="BJ13" s="113"/>
+      <c r="BK13" s="113"/>
+      <c r="BL13" s="113"/>
+      <c r="BM13" s="113"/>
+      <c r="BN13" s="113"/>
+      <c r="BO13" s="113"/>
+      <c r="BP13" s="113"/>
+      <c r="BQ13" s="113"/>
+      <c r="BR13" s="113"/>
+      <c r="BS13" s="113"/>
+      <c r="BT13" s="113"/>
+      <c r="BU13" s="64" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="14" spans="1:79" ht="14.4">
+    <row r="14" spans="1:79">
       <c r="A14" s="100"/>
       <c r="B14" s="100"/>
       <c r="C14" s="100"/>
@@ -3347,25 +3388,25 @@
       <c r="G14" s="100"/>
       <c r="H14" s="100"/>
       <c r="I14" s="100"/>
-      <c r="AR14" s="53" t="s">
+      <c r="AR14" s="52" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:79" ht="14.4">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:79">
+      <c r="A15" s="33" t="s">
         <v>82</v>
       </c>
       <c r="H15" s="100"/>
       <c r="I15" s="100"/>
-      <c r="J15" s="34" t="s">
+      <c r="J15" s="33" t="s">
         <v>99</v>
       </c>
       <c r="R15" s="100"/>
       <c r="S15" s="100"/>
-      <c r="T15" s="34" t="s">
+      <c r="T15" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="AR15" s="53" t="s">
+      <c r="AR15" s="52" t="s">
         <v>143</v>
       </c>
     </row>
@@ -3374,7 +3415,7 @@
       <c r="B16" s="100"/>
       <c r="C16" s="100"/>
       <c r="D16" s="100"/>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="33" t="s">
         <v>101</v>
       </c>
       <c r="H16" s="100"/>
@@ -3382,10 +3423,10 @@
       <c r="J16" s="100"/>
       <c r="K16" s="100"/>
       <c r="L16" s="100"/>
-      <c r="M16" s="34" t="s">
+      <c r="M16" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AR16" s="53" t="s">
+      <c r="AR16" s="52" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3399,17 +3440,17 @@
       <c r="G17" s="100"/>
       <c r="H17" s="100"/>
       <c r="I17" s="100"/>
-      <c r="AR17" s="53" t="s">
+      <c r="AR17" s="52" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:44">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="33" t="s">
         <v>102</v>
       </c>
       <c r="L18" s="100"/>
       <c r="M18" s="100"/>
-      <c r="N18" s="34" t="s">
+      <c r="N18" s="33" t="s">
         <v>103</v>
       </c>
       <c r="P18" s="100"/>
@@ -3418,40 +3459,40 @@
       <c r="S18" s="100"/>
       <c r="T18" s="100"/>
       <c r="U18" s="100"/>
-      <c r="V18" s="34" t="s">
+      <c r="V18" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="AR18" s="53" t="s">
+      <c r="AR18" s="52" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="14.4">
-      <c r="A19" s="34" t="s">
+    <row r="19" spans="1:44">
+      <c r="A19" s="33" t="s">
         <v>92</v>
       </c>
       <c r="E19" s="100"/>
       <c r="F19" s="100"/>
-      <c r="G19" s="34" t="s">
+      <c r="G19" s="33" t="s">
         <v>99</v>
       </c>
       <c r="O19" s="100"/>
       <c r="P19" s="100"/>
-      <c r="Q19" s="34" t="s">
+      <c r="Q19" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="AR19" s="53" t="s">
+      <c r="AR19" s="52" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:44">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="33" t="s">
         <v>106</v>
       </c>
       <c r="F20" s="100"/>
       <c r="G20" s="100"/>
       <c r="H20" s="100"/>
       <c r="I20" s="100"/>
-      <c r="J20" s="34" t="s">
+      <c r="J20" s="33" t="s">
         <v>101</v>
       </c>
       <c r="M20" s="100"/>
@@ -3459,99 +3500,99 @@
       <c r="O20" s="100"/>
       <c r="P20" s="100"/>
       <c r="Q20" s="100"/>
-      <c r="R20" s="34" t="s">
+      <c r="R20" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AR20" s="53" t="s">
+      <c r="AR20" s="52" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:44">
-      <c r="AR21" s="53" t="s">
+      <c r="AR21" s="52" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:44">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="33" t="s">
         <v>107</v>
       </c>
       <c r="K22" s="100"/>
       <c r="L22" s="100"/>
-      <c r="M22" s="34" t="s">
+      <c r="M22" s="33" t="s">
         <v>108</v>
       </c>
       <c r="Q22" s="100"/>
       <c r="R22" s="100"/>
-      <c r="S22" s="34" t="s">
+      <c r="S22" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="AR22" s="53" t="s">
+      <c r="AR22" s="52" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:44">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="AR23" s="53" t="s">
+      <c r="AR23" s="52" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:44">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="33" t="s">
         <v>111</v>
       </c>
       <c r="E24" s="100"/>
       <c r="F24" s="100"/>
       <c r="G24" s="100"/>
       <c r="H24" s="100"/>
-      <c r="I24" s="34" t="s">
+      <c r="I24" s="33" t="s">
         <v>112</v>
       </c>
       <c r="K24" s="100"/>
       <c r="L24" s="100"/>
-      <c r="M24" s="34" t="s">
+      <c r="M24" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AR24" s="53" t="s">
+      <c r="AR24" s="52" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:44">
-      <c r="AR25" s="53" t="s">
+      <c r="AR25" s="52" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:44">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="33" t="s">
         <v>113</v>
       </c>
       <c r="M26" s="100"/>
       <c r="N26" s="100"/>
-      <c r="O26" s="34" t="s">
+      <c r="O26" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="AR26" s="53" t="s">
+      <c r="AR26" s="52" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:44">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="33" t="s">
         <v>115</v>
       </c>
       <c r="X27" s="100"/>
       <c r="Y27" s="100"/>
       <c r="Z27" s="100"/>
       <c r="AA27" s="100"/>
-      <c r="AB27" s="34" t="s">
+      <c r="AB27" s="33" t="s">
         <v>112</v>
       </c>
       <c r="AD27" s="100"/>
       <c r="AE27" s="100"/>
-      <c r="AF27" s="34" t="s">
+      <c r="AF27" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="AR27" s="53" t="s">
+      <c r="AR27" s="52" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3560,25 +3601,25 @@
       <c r="B28" s="100"/>
       <c r="C28" s="100"/>
       <c r="D28" s="100"/>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="33" t="s">
         <v>112</v>
       </c>
       <c r="G28" s="100"/>
       <c r="H28" s="100"/>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AR28" s="53" t="s">
+      <c r="AR28" s="52" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:44">
-      <c r="AR29" s="53" t="s">
+      <c r="AR29" s="52" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:44">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="33" t="s">
         <v>117</v>
       </c>
       <c r="K30" s="100"/>
@@ -3595,12 +3636,12 @@
       <c r="V30" s="100"/>
       <c r="W30" s="100"/>
       <c r="X30" s="100"/>
-      <c r="AR30" s="53" t="s">
+      <c r="AR30" s="52" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:44">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="33" t="s">
         <v>41</v>
       </c>
       <c r="G31" s="100"/>
@@ -3617,37 +3658,37 @@
       <c r="S31" s="100"/>
       <c r="T31" s="100"/>
       <c r="U31" s="100"/>
-      <c r="V31" s="34" t="s">
+      <c r="V31" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="AR31" s="53" t="s">
+      <c r="AR31" s="52" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:44">
-      <c r="AR32" s="53" t="s">
+      <c r="AR32" s="52" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:79">
-      <c r="AR33" s="53" t="s">
+      <c r="AR33" s="52" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:79">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="33" t="s">
         <v>4</v>
       </c>
       <c r="G34" s="103"/>
       <c r="H34" s="103"/>
       <c r="I34" s="103"/>
-      <c r="W34" s="34" t="s">
+      <c r="W34" s="33" t="s">
         <v>4</v>
       </c>
       <c r="AC34" s="103"/>
       <c r="AD34" s="103"/>
       <c r="AE34" s="103"/>
-      <c r="AR34" s="34" t="s">
+      <c r="AR34" s="33" t="s">
         <v>161</v>
       </c>
     </row>
@@ -3655,123 +3696,123 @@
       <c r="A35" s="97"/>
       <c r="B35" s="95"/>
       <c r="C35" s="96"/>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="42" t="s">
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="44"/>
-      <c r="N35" s="43" t="s">
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="44"/>
-      <c r="S35" s="43" t="s">
+      <c r="O35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="44"/>
-      <c r="X35" s="43" t="s">
+      <c r="T35" s="42"/>
+      <c r="U35" s="42"/>
+      <c r="V35" s="42"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="Y35" s="43"/>
-      <c r="Z35" s="43"/>
-      <c r="AA35" s="43"/>
-      <c r="AB35" s="44"/>
-      <c r="AC35" s="43" t="s">
+      <c r="Y35" s="42"/>
+      <c r="Z35" s="42"/>
+      <c r="AA35" s="42"/>
+      <c r="AB35" s="43"/>
+      <c r="AC35" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="AD35" s="43"/>
-      <c r="AE35" s="43"/>
-      <c r="AF35" s="43"/>
-      <c r="AG35" s="44"/>
-      <c r="AH35" s="43" t="s">
+      <c r="AD35" s="42"/>
+      <c r="AE35" s="42"/>
+      <c r="AF35" s="42"/>
+      <c r="AG35" s="43"/>
+      <c r="AH35" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AI35" s="43"/>
-      <c r="AJ35" s="43"/>
-      <c r="AK35" s="43"/>
-      <c r="AL35" s="44"/>
-      <c r="AM35" s="43" t="s">
+      <c r="AI35" s="42"/>
+      <c r="AJ35" s="42"/>
+      <c r="AK35" s="42"/>
+      <c r="AL35" s="43"/>
+      <c r="AM35" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="AN35" s="43"/>
-      <c r="AO35" s="43"/>
-      <c r="AP35" s="44"/>
-      <c r="AR35" s="55"/>
+      <c r="AN35" s="42"/>
+      <c r="AO35" s="42"/>
+      <c r="AP35" s="43"/>
+      <c r="AR35" s="54"/>
     </row>
     <row r="36" spans="1:79">
       <c r="A36" s="104"/>
       <c r="B36" s="101"/>
       <c r="C36" s="105"/>
-      <c r="D36" s="45" t="s">
+      <c r="D36" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="45" t="s">
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="44"/>
-      <c r="N36" s="43" t="s">
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="43"/>
-      <c r="R36" s="44"/>
-      <c r="S36" s="43" t="s">
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="T36" s="43"/>
-      <c r="U36" s="43"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="44"/>
-      <c r="X36" s="44" t="s">
+      <c r="T36" s="42"/>
+      <c r="U36" s="42"/>
+      <c r="V36" s="42"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="Y36" s="43"/>
-      <c r="Z36" s="43"/>
-      <c r="AA36" s="43"/>
-      <c r="AB36" s="44"/>
-      <c r="AC36" s="44" t="s">
+      <c r="Y36" s="42"/>
+      <c r="Z36" s="42"/>
+      <c r="AA36" s="42"/>
+      <c r="AB36" s="43"/>
+      <c r="AC36" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="AD36" s="43"/>
-      <c r="AE36" s="43"/>
-      <c r="AF36" s="43"/>
-      <c r="AG36" s="44"/>
-      <c r="AH36" s="44" t="s">
+      <c r="AD36" s="42"/>
+      <c r="AE36" s="42"/>
+      <c r="AF36" s="42"/>
+      <c r="AG36" s="43"/>
+      <c r="AH36" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AI36" s="43"/>
-      <c r="AJ36" s="43"/>
-      <c r="AK36" s="43"/>
-      <c r="AL36" s="44"/>
-      <c r="AM36" s="44" t="s">
+      <c r="AI36" s="42"/>
+      <c r="AJ36" s="42"/>
+      <c r="AK36" s="42"/>
+      <c r="AL36" s="43"/>
+      <c r="AM36" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AN36" s="43"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="44"/>
-      <c r="AR36" s="55" t="s">
+      <c r="AN36" s="42"/>
+      <c r="AO36" s="42"/>
+      <c r="AP36" s="43"/>
+      <c r="AR36" s="54" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3866,7 +3907,7 @@
       <c r="AN38" s="110"/>
       <c r="AO38" s="110"/>
       <c r="AP38" s="111"/>
-      <c r="AR38" s="34" t="s">
+      <c r="AR38" s="33" t="s">
         <v>171</v>
       </c>
       <c r="AS38" s="13"/>
@@ -3881,7 +3922,7 @@
       <c r="BB38" s="92"/>
       <c r="BC38" s="92"/>
       <c r="BD38" s="92"/>
-      <c r="BE38" s="77" t="s">
+      <c r="BE38" s="76" t="s">
         <v>208</v>
       </c>
       <c r="BF38" s="13"/>
@@ -3896,7 +3937,7 @@
       <c r="BO38" s="92"/>
       <c r="BP38" s="92"/>
       <c r="BQ38" s="92"/>
-      <c r="BR38" s="34" t="s">
+      <c r="BR38" s="33" t="s">
         <v>224</v>
       </c>
     </row>
@@ -3945,7 +3986,7 @@
       <c r="AN39" s="110"/>
       <c r="AO39" s="110"/>
       <c r="AP39" s="111"/>
-      <c r="AR39" s="34" t="s">
+      <c r="AR39" s="33" t="s">
         <v>209</v>
       </c>
       <c r="AV39" s="92"/>
@@ -3962,7 +4003,7 @@
       <c r="BG39" s="92"/>
       <c r="BH39" s="92"/>
       <c r="BI39" s="92"/>
-      <c r="BJ39" s="61" t="s">
+      <c r="BJ39" s="60" t="s">
         <v>217</v>
       </c>
       <c r="BT39" s="93"/>
@@ -4087,19 +4128,19 @@
       <c r="AP41" s="105"/>
     </row>
     <row r="42" spans="1:79" ht="15" customHeight="1">
-      <c r="A42" s="52"/>
-      <c r="AR42" s="34" t="s">
+      <c r="A42" s="51"/>
+      <c r="AR42" s="33" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:79" ht="15" customHeight="1">
-      <c r="A43" s="34" t="s">
+      <c r="A43" s="33" t="s">
         <v>4</v>
       </c>
       <c r="G43" s="103"/>
       <c r="H43" s="103"/>
       <c r="I43" s="103"/>
-      <c r="W43" s="34" t="s">
+      <c r="W43" s="33" t="s">
         <v>4</v>
       </c>
       <c r="AC43" s="103"/>
@@ -4110,121 +4151,121 @@
       <c r="A44" s="97"/>
       <c r="B44" s="95"/>
       <c r="C44" s="96"/>
-      <c r="D44" s="42" t="s">
+      <c r="D44" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="42" t="s">
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="43"/>
-      <c r="M44" s="44"/>
-      <c r="N44" s="43" t="s">
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="43"/>
+      <c r="N44" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="43"/>
-      <c r="P44" s="43"/>
-      <c r="Q44" s="43"/>
-      <c r="R44" s="44"/>
-      <c r="S44" s="43" t="s">
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
+      <c r="S44" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="T44" s="43"/>
-      <c r="U44" s="43"/>
-      <c r="V44" s="43"/>
-      <c r="W44" s="44"/>
-      <c r="X44" s="43" t="s">
+      <c r="T44" s="42"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="43"/>
+      <c r="X44" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="Y44" s="43"/>
-      <c r="Z44" s="43"/>
-      <c r="AA44" s="43"/>
-      <c r="AB44" s="44"/>
-      <c r="AC44" s="43" t="s">
+      <c r="Y44" s="42"/>
+      <c r="Z44" s="42"/>
+      <c r="AA44" s="42"/>
+      <c r="AB44" s="43"/>
+      <c r="AC44" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="AD44" s="43"/>
-      <c r="AE44" s="43"/>
-      <c r="AF44" s="43"/>
-      <c r="AG44" s="44"/>
-      <c r="AH44" s="43" t="s">
+      <c r="AD44" s="42"/>
+      <c r="AE44" s="42"/>
+      <c r="AF44" s="42"/>
+      <c r="AG44" s="43"/>
+      <c r="AH44" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AI44" s="43"/>
-      <c r="AJ44" s="43"/>
-      <c r="AK44" s="43"/>
-      <c r="AL44" s="44"/>
-      <c r="AM44" s="43" t="s">
+      <c r="AI44" s="42"/>
+      <c r="AJ44" s="42"/>
+      <c r="AK44" s="42"/>
+      <c r="AL44" s="43"/>
+      <c r="AM44" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="AN44" s="43"/>
-      <c r="AO44" s="43"/>
-      <c r="AP44" s="44"/>
+      <c r="AN44" s="42"/>
+      <c r="AO44" s="42"/>
+      <c r="AP44" s="43"/>
     </row>
     <row r="45" spans="1:79" ht="15" customHeight="1">
       <c r="A45" s="104"/>
       <c r="B45" s="101"/>
       <c r="C45" s="105"/>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="45" t="s">
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="44"/>
-      <c r="N45" s="43" t="s">
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="43"/>
+      <c r="N45" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="O45" s="43"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="43" t="s">
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="T45" s="43"/>
-      <c r="U45" s="43"/>
-      <c r="V45" s="43"/>
-      <c r="W45" s="44"/>
-      <c r="X45" s="44" t="s">
+      <c r="T45" s="42"/>
+      <c r="U45" s="42"/>
+      <c r="V45" s="42"/>
+      <c r="W45" s="43"/>
+      <c r="X45" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="Y45" s="43"/>
-      <c r="Z45" s="43"/>
-      <c r="AA45" s="43"/>
-      <c r="AB45" s="44"/>
-      <c r="AC45" s="44" t="s">
+      <c r="Y45" s="42"/>
+      <c r="Z45" s="42"/>
+      <c r="AA45" s="42"/>
+      <c r="AB45" s="43"/>
+      <c r="AC45" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="AD45" s="43"/>
-      <c r="AE45" s="43"/>
-      <c r="AF45" s="43"/>
-      <c r="AG45" s="44"/>
-      <c r="AH45" s="44" t="s">
+      <c r="AD45" s="42"/>
+      <c r="AE45" s="42"/>
+      <c r="AF45" s="42"/>
+      <c r="AG45" s="43"/>
+      <c r="AH45" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AI45" s="43"/>
-      <c r="AJ45" s="43"/>
-      <c r="AK45" s="43"/>
-      <c r="AL45" s="44"/>
-      <c r="AM45" s="44" t="s">
+      <c r="AI45" s="42"/>
+      <c r="AJ45" s="42"/>
+      <c r="AK45" s="42"/>
+      <c r="AL45" s="43"/>
+      <c r="AM45" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AN45" s="43"/>
-      <c r="AO45" s="43"/>
-      <c r="AP45" s="44"/>
+      <c r="AN45" s="42"/>
+      <c r="AO45" s="42"/>
+      <c r="AP45" s="43"/>
     </row>
     <row r="46" spans="1:79" ht="15" customHeight="1">
       <c r="A46" s="106" t="s">
@@ -4549,7 +4590,7 @@
       <c r="AP52" s="96"/>
     </row>
     <row r="54" spans="1:42">
-      <c r="A54" s="34" t="s">
+      <c r="A54" s="33" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4574,7 +4615,7 @@
     <mergeCell ref="BJ8:BM8"/>
     <mergeCell ref="BA6:BD6"/>
     <mergeCell ref="BJ6:BM6"/>
-    <mergeCell ref="BI13:BJ13"/>
+    <mergeCell ref="BI13:BL13"/>
     <mergeCell ref="A52:AP52"/>
     <mergeCell ref="AM49:AP51"/>
     <mergeCell ref="A50:C50"/>
@@ -4733,7 +4774,7 @@
     <mergeCell ref="BA7:BD7"/>
     <mergeCell ref="BH38:BQ38"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -4757,60 +4798,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03BF3F4D-D8CD-4618-AB53-5E09294BE46F}">
   <dimension ref="A1:CA74"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="3" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="1.6640625" style="34" hidden="1" customWidth="1"/>
-    <col min="5" max="6" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="1.88671875" style="34" hidden="1" customWidth="1"/>
-    <col min="8" max="13" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="1.44140625" style="34" hidden="1" customWidth="1"/>
-    <col min="15" max="42" width="2" style="34" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="2.33203125" style="34" hidden="1" customWidth="1"/>
-    <col min="44" max="79" width="2.33203125" style="34" customWidth="1"/>
-    <col min="80" max="16384" width="8.88671875" style="34"/>
+    <col min="1" max="3" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="1.640625" style="33" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" style="33" hidden="1" customWidth="1"/>
+    <col min="8" max="13" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="33" hidden="1" customWidth="1"/>
+    <col min="15" max="42" width="2" style="33" hidden="1" customWidth="1"/>
+    <col min="43" max="43" width="2.35546875" style="33" hidden="1" customWidth="1"/>
+    <col min="44" max="51" width="2.35546875" style="33" customWidth="1"/>
+    <col min="52" max="52" width="2.85546875" style="33" customWidth="1"/>
+    <col min="53" max="68" width="2.35546875" style="33" customWidth="1"/>
+    <col min="69" max="69" width="2.2109375" style="33" customWidth="1"/>
+    <col min="70" max="70" width="2.640625" style="33" customWidth="1"/>
+    <col min="71" max="79" width="2.35546875" style="33" customWidth="1"/>
+    <col min="80" max="16384" width="8.85546875" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:79">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="AR1" s="34" t="s">
+      <c r="AR1" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="BC1" s="112"/>
-      <c r="BD1" s="112"/>
-      <c r="BE1" s="112"/>
-      <c r="BF1" s="112"/>
-      <c r="BG1" s="112"/>
-      <c r="BH1" s="112"/>
-      <c r="BI1" s="112"/>
-      <c r="BJ1" s="112"/>
-      <c r="BK1" s="112"/>
-      <c r="BL1" s="112"/>
-      <c r="BM1" s="112"/>
-      <c r="BN1" s="112"/>
-      <c r="BO1" s="112"/>
-      <c r="BP1" s="112"/>
-      <c r="BQ1" s="112"/>
-      <c r="BR1" s="112"/>
-      <c r="BS1" s="112"/>
-      <c r="BT1" s="112"/>
-      <c r="BU1" s="112"/>
-      <c r="BV1" s="112"/>
-      <c r="BW1" s="112"/>
-      <c r="BX1" s="112"/>
-      <c r="BY1" s="112"/>
-      <c r="BZ1" s="112"/>
-      <c r="CA1" s="112"/>
+      <c r="BC1" s="113"/>
+      <c r="BD1" s="113"/>
+      <c r="BE1" s="113"/>
+      <c r="BF1" s="113"/>
+      <c r="BG1" s="113"/>
+      <c r="BH1" s="113"/>
+      <c r="BI1" s="113"/>
+      <c r="BJ1" s="113"/>
+      <c r="BK1" s="113"/>
+      <c r="BL1" s="113"/>
+      <c r="BM1" s="113"/>
+      <c r="BN1" s="113"/>
+      <c r="BO1" s="113"/>
+      <c r="BP1" s="113"/>
+      <c r="BQ1" s="113"/>
+      <c r="BR1" s="113"/>
+      <c r="BS1" s="113"/>
+      <c r="BT1" s="113"/>
+      <c r="BU1" s="113"/>
+      <c r="BV1" s="113"/>
+      <c r="BW1" s="113"/>
+      <c r="BX1" s="113"/>
+      <c r="BY1" s="113"/>
+      <c r="BZ1" s="113"/>
+      <c r="CA1" s="113"/>
     </row>
     <row r="2" spans="1:79">
-      <c r="AR2" s="35" t="s">
+      <c r="AR2" s="34" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:79">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>81</v>
       </c>
       <c r="AR3" s="94"/>
@@ -4841,9 +4887,9 @@
       <c r="BQ3" s="94"/>
       <c r="BR3" s="94"/>
       <c r="BS3" s="94"/>
-      <c r="BY3" s="35"/>
-      <c r="BZ3" s="35"/>
-      <c r="CA3" s="35"/>
+      <c r="BY3" s="34"/>
+      <c r="BZ3" s="34"/>
+      <c r="CA3" s="34"/>
     </row>
     <row r="4" spans="1:79">
       <c r="A4" s="100"/>
@@ -4855,7 +4901,7 @@
       <c r="G4" s="100"/>
       <c r="H4" s="100"/>
       <c r="I4" s="100"/>
-      <c r="AR4" s="34" t="s">
+      <c r="AR4" s="33" t="s">
         <v>171</v>
       </c>
       <c r="AS4" s="13"/>
@@ -4866,49 +4912,49 @@
       <c r="AX4" s="13"/>
       <c r="AY4" s="13"/>
       <c r="AZ4" s="13"/>
-      <c r="BA4" s="114"/>
-      <c r="BB4" s="114"/>
-      <c r="BC4" s="114"/>
-      <c r="BD4" s="114"/>
-      <c r="BE4" s="77" t="s">
+      <c r="BA4" s="115"/>
+      <c r="BB4" s="115"/>
+      <c r="BC4" s="115"/>
+      <c r="BD4" s="115"/>
+      <c r="BE4" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="BF4" s="78"/>
-      <c r="BG4" s="77"/>
-      <c r="BH4" s="114"/>
-      <c r="BI4" s="114"/>
-      <c r="BJ4" s="114"/>
-      <c r="BK4" s="114"/>
-      <c r="BL4" s="114"/>
-      <c r="BM4" s="114"/>
-      <c r="BN4" s="114"/>
-      <c r="BO4" s="114"/>
-      <c r="BP4" s="114"/>
-      <c r="BQ4" s="114"/>
-      <c r="BR4" s="114"/>
-      <c r="BS4" s="34" t="s">
+      <c r="BF4" s="77"/>
+      <c r="BG4" s="76"/>
+      <c r="BH4" s="115"/>
+      <c r="BI4" s="115"/>
+      <c r="BJ4" s="115"/>
+      <c r="BK4" s="115"/>
+      <c r="BL4" s="115"/>
+      <c r="BM4" s="115"/>
+      <c r="BN4" s="115"/>
+      <c r="BO4" s="115"/>
+      <c r="BP4" s="115"/>
+      <c r="BQ4" s="115"/>
+      <c r="BR4" s="115"/>
+      <c r="BS4" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="BY4" s="35"/>
-      <c r="BZ4" s="35"/>
-      <c r="CA4" s="35"/>
+      <c r="BY4" s="34"/>
+      <c r="BZ4" s="34"/>
+      <c r="CA4" s="34"/>
     </row>
     <row r="5" spans="1:79">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>82</v>
       </c>
       <c r="H5" s="100"/>
       <c r="I5" s="100"/>
-      <c r="J5" s="34" t="s">
+      <c r="J5" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="AE5" s="34" t="s">
+      <c r="AE5" s="33" t="s">
         <v>84</v>
       </c>
       <c r="AM5" s="101"/>
       <c r="AN5" s="101"/>
-      <c r="AO5" s="36"/>
-      <c r="AR5" s="34" t="s">
+      <c r="AO5" s="35"/>
+      <c r="AR5" s="33" t="s">
         <v>209</v>
       </c>
       <c r="AV5" s="92"/>
@@ -4921,121 +4967,123 @@
       <c r="BC5" s="92"/>
       <c r="BD5" s="92"/>
       <c r="BE5" s="92"/>
-      <c r="BF5" s="61" t="s">
+      <c r="BF5" s="60" t="s">
         <v>172</v>
       </c>
-      <c r="BG5" s="61"/>
+      <c r="BG5" s="60"/>
       <c r="BH5" s="13"/>
       <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
-      <c r="BK5" s="61"/>
-      <c r="BL5" s="33"/>
-      <c r="BM5" s="33"/>
-      <c r="BN5" s="33"/>
-      <c r="BO5" s="33"/>
-      <c r="BP5" s="112"/>
-      <c r="BQ5" s="112"/>
-      <c r="BR5" s="112"/>
-      <c r="BS5" s="112"/>
-      <c r="BT5" s="112"/>
-      <c r="BU5" s="112"/>
-      <c r="BV5" s="112"/>
-      <c r="BW5" s="112"/>
-      <c r="BX5" s="34" t="s">
+      <c r="BK5" s="60"/>
+      <c r="BL5" s="32"/>
+      <c r="BM5" s="32"/>
+      <c r="BN5" s="32"/>
+      <c r="BO5" s="32"/>
+      <c r="BP5" s="113"/>
+      <c r="BQ5" s="113"/>
+      <c r="BR5" s="113"/>
+      <c r="BS5" s="113"/>
+      <c r="BT5" s="113"/>
+      <c r="BU5" s="113"/>
+      <c r="BV5" s="113"/>
+      <c r="BW5" s="113"/>
+      <c r="BX5" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="BY5" s="85" t="s">
+      <c r="BY5" s="83" t="s">
         <v>205</v>
       </c>
-      <c r="BZ5" s="61" t="s">
+      <c r="BZ5" s="60" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:79">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="33" t="s">
         <v>90</v>
       </c>
       <c r="N6" s="100"/>
       <c r="O6" s="100"/>
       <c r="P6" s="100"/>
       <c r="Q6" s="100"/>
-      <c r="R6" s="36" t="s">
+      <c r="R6" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="S6" s="34" t="s">
+      <c r="S6" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AR6" s="115"/>
-      <c r="AS6" s="115"/>
-      <c r="AT6" s="115"/>
-      <c r="AU6" s="115"/>
-      <c r="AV6" s="115"/>
-      <c r="AW6" s="115"/>
-      <c r="AX6" s="115"/>
-      <c r="AY6" s="115"/>
-      <c r="AZ6" s="115"/>
-      <c r="BA6" s="115"/>
-      <c r="BB6" s="115"/>
-      <c r="BC6" s="115"/>
-      <c r="BD6" s="115"/>
-      <c r="BE6" s="115"/>
-      <c r="BF6" s="115"/>
-      <c r="BG6" s="115"/>
-      <c r="BH6" s="63"/>
-      <c r="BI6" s="38"/>
-      <c r="BJ6" s="38"/>
-      <c r="BK6" s="38"/>
-      <c r="BL6" s="38"/>
-      <c r="BM6" s="38"/>
+      <c r="AR6" s="116"/>
+      <c r="AS6" s="116"/>
+      <c r="AT6" s="116"/>
+      <c r="AU6" s="116"/>
+      <c r="AV6" s="116"/>
+      <c r="AW6" s="116"/>
+      <c r="AX6" s="116"/>
+      <c r="AY6" s="116"/>
+      <c r="AZ6" s="116"/>
+      <c r="BA6" s="116"/>
+      <c r="BB6" s="116"/>
+      <c r="BC6" s="116"/>
+      <c r="BD6" s="116"/>
+      <c r="BE6" s="116"/>
+      <c r="BF6" s="116"/>
+      <c r="BG6" s="116"/>
+      <c r="BH6" s="208" t="s">
+        <v>228</v>
+      </c>
+      <c r="BI6" s="37"/>
+      <c r="BJ6" s="113"/>
+      <c r="BK6" s="113"/>
+      <c r="BL6" s="113"/>
+      <c r="BM6" s="113"/>
       <c r="BN6" s="13"/>
-      <c r="BQ6" s="79" t="s">
+      <c r="BQ6" s="78" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:79">
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="36"/>
-      <c r="AR7" s="116" t="s">
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="35"/>
+      <c r="AR7" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="AS7" s="116"/>
-      <c r="AT7" s="116"/>
-      <c r="AU7" s="116"/>
-      <c r="AV7" s="116"/>
-      <c r="AW7" s="116"/>
-      <c r="AX7" s="116"/>
-      <c r="AY7" s="116"/>
-      <c r="AZ7" s="117"/>
-      <c r="BA7" s="117"/>
-      <c r="BB7" s="117"/>
-      <c r="BC7" s="117"/>
-      <c r="BD7" s="117"/>
-      <c r="BE7" s="117"/>
-      <c r="BF7" s="117"/>
-      <c r="BG7" s="117"/>
-      <c r="BH7" s="117"/>
-      <c r="BI7" s="117"/>
-      <c r="BJ7" s="117"/>
-      <c r="BK7" s="117"/>
-      <c r="BL7" s="117"/>
-      <c r="BM7" s="117"/>
-      <c r="BN7" s="117"/>
-      <c r="BO7" s="117"/>
-      <c r="BP7" s="117"/>
-      <c r="BQ7" s="117"/>
-      <c r="BR7" s="117"/>
-      <c r="BS7" s="117"/>
-      <c r="BT7" s="117"/>
-      <c r="BU7" s="117"/>
-      <c r="BV7" s="117"/>
-      <c r="BW7" s="117"/>
-      <c r="BX7" s="117"/>
-      <c r="BY7" s="117"/>
-      <c r="BZ7" s="117"/>
-      <c r="CA7" s="117"/>
+      <c r="AS7" s="117"/>
+      <c r="AT7" s="117"/>
+      <c r="AU7" s="117"/>
+      <c r="AV7" s="117"/>
+      <c r="AW7" s="117"/>
+      <c r="AX7" s="117"/>
+      <c r="AY7" s="117"/>
+      <c r="AZ7" s="118"/>
+      <c r="BA7" s="118"/>
+      <c r="BB7" s="118"/>
+      <c r="BC7" s="118"/>
+      <c r="BD7" s="118"/>
+      <c r="BE7" s="118"/>
+      <c r="BF7" s="118"/>
+      <c r="BG7" s="118"/>
+      <c r="BH7" s="118"/>
+      <c r="BI7" s="118"/>
+      <c r="BJ7" s="118"/>
+      <c r="BK7" s="118"/>
+      <c r="BL7" s="118"/>
+      <c r="BM7" s="118"/>
+      <c r="BN7" s="118"/>
+      <c r="BO7" s="118"/>
+      <c r="BP7" s="118"/>
+      <c r="BQ7" s="118"/>
+      <c r="BR7" s="118"/>
+      <c r="BS7" s="118"/>
+      <c r="BT7" s="118"/>
+      <c r="BU7" s="118"/>
+      <c r="BV7" s="118"/>
+      <c r="BW7" s="118"/>
+      <c r="BX7" s="118"/>
+      <c r="BY7" s="118"/>
+      <c r="BZ7" s="118"/>
+      <c r="CA7" s="118"/>
     </row>
     <row r="8" spans="1:79">
       <c r="A8" s="100"/>
@@ -5047,215 +5095,226 @@
       <c r="G8" s="100"/>
       <c r="H8" s="100"/>
       <c r="I8" s="100"/>
-      <c r="AR8" s="116" t="s">
+      <c r="AR8" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="AS8" s="116"/>
-      <c r="AT8" s="116"/>
-      <c r="AU8" s="116"/>
-      <c r="AV8" s="116"/>
-      <c r="AW8" s="116"/>
-      <c r="AX8" s="116"/>
-      <c r="AY8" s="116"/>
-      <c r="AZ8" s="116"/>
-      <c r="BA8" s="116"/>
-      <c r="BB8" s="116"/>
-      <c r="BC8" s="116"/>
-      <c r="BD8" s="116"/>
-      <c r="BE8" s="116"/>
-      <c r="BF8" s="116"/>
-      <c r="BG8" s="116"/>
-      <c r="BH8" s="116"/>
-      <c r="BI8" s="116"/>
-      <c r="BJ8" s="116"/>
-      <c r="BK8" s="116"/>
-      <c r="BL8" s="116"/>
-      <c r="BM8" s="116"/>
-      <c r="BN8" s="116"/>
-      <c r="BO8" s="116"/>
-      <c r="BP8" s="116"/>
-      <c r="BQ8" s="116"/>
-      <c r="BR8" s="116"/>
-      <c r="BS8" s="116"/>
-      <c r="BT8" s="116"/>
-      <c r="BU8" s="116"/>
-      <c r="BV8" s="116"/>
-      <c r="BW8" s="116"/>
-      <c r="BX8" s="116"/>
-      <c r="BY8" s="116"/>
-      <c r="BZ8" s="116"/>
-      <c r="CA8" s="116"/>
+      <c r="AS8" s="117"/>
+      <c r="AT8" s="117"/>
+      <c r="AU8" s="117"/>
+      <c r="AV8" s="117"/>
+      <c r="AW8" s="117"/>
+      <c r="AX8" s="117"/>
+      <c r="AY8" s="117"/>
+      <c r="AZ8" s="117"/>
+      <c r="BA8" s="117"/>
+      <c r="BB8" s="117"/>
+      <c r="BC8" s="117"/>
+      <c r="BD8" s="117"/>
+      <c r="BE8" s="117"/>
+      <c r="BF8" s="117"/>
+      <c r="BG8" s="117"/>
+      <c r="BH8" s="117"/>
+      <c r="BI8" s="117"/>
+      <c r="BJ8" s="117"/>
+      <c r="BK8" s="117"/>
+      <c r="BL8" s="117"/>
+      <c r="BM8" s="117"/>
+      <c r="BN8" s="117"/>
+      <c r="BO8" s="117"/>
+      <c r="BP8" s="117"/>
+      <c r="BQ8" s="117"/>
+      <c r="BR8" s="117"/>
+      <c r="BS8" s="117"/>
+      <c r="BT8" s="117"/>
+      <c r="BU8" s="117"/>
+      <c r="BV8" s="117"/>
+      <c r="BW8" s="117"/>
+      <c r="BX8" s="117"/>
+      <c r="BY8" s="117"/>
+      <c r="BZ8" s="117"/>
+      <c r="CA8" s="117"/>
     </row>
     <row r="9" spans="1:79">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="39" t="s">
         <v>3</v>
       </c>
       <c r="H9" s="102"/>
       <c r="I9" s="102"/>
       <c r="K9" s="101"/>
       <c r="L9" s="101"/>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="O9" s="40" t="s">
+      <c r="O9" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="P9" s="33" t="s">
         <v>84</v>
       </c>
       <c r="X9" s="100"/>
       <c r="Y9" s="100"/>
-      <c r="Z9" s="34" t="s">
+      <c r="Z9" s="33" t="s">
         <v>94</v>
       </c>
       <c r="AI9" s="100"/>
       <c r="AJ9" s="100"/>
-      <c r="AK9" s="34" t="s">
+      <c r="AK9" s="33" t="s">
         <v>95</v>
       </c>
       <c r="AN9" s="100"/>
       <c r="AO9" s="100"/>
       <c r="AP9" s="100"/>
-      <c r="AR9" s="116" t="s">
+      <c r="AR9" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="AS9" s="116"/>
-      <c r="AT9" s="116"/>
-      <c r="AU9" s="116"/>
-      <c r="AV9" s="116"/>
-      <c r="AW9" s="116"/>
-      <c r="AX9" s="116"/>
-      <c r="AY9" s="116"/>
-      <c r="AZ9" s="116"/>
-      <c r="BA9" s="116"/>
-      <c r="BB9" s="116"/>
-      <c r="BC9" s="116"/>
-      <c r="BD9" s="116"/>
-      <c r="BE9" s="116"/>
-      <c r="BF9" s="116"/>
-      <c r="BG9" s="116"/>
-      <c r="BH9" s="116"/>
-      <c r="BI9" s="116"/>
-      <c r="BJ9" s="116"/>
-      <c r="BK9" s="116"/>
-      <c r="BL9" s="116"/>
-      <c r="BM9" s="116"/>
-      <c r="BN9" s="116"/>
-      <c r="BO9" s="116"/>
-      <c r="BP9" s="116"/>
-      <c r="BQ9" s="116"/>
-      <c r="BR9" s="116"/>
-      <c r="BS9" s="116"/>
-      <c r="BT9" s="116"/>
-      <c r="BU9" s="116"/>
-      <c r="BV9" s="116"/>
-      <c r="BW9" s="116"/>
-      <c r="BX9" s="116"/>
-      <c r="BY9" s="116"/>
-      <c r="BZ9" s="116"/>
-      <c r="CA9" s="116"/>
+      <c r="AS9" s="117"/>
+      <c r="AT9" s="117"/>
+      <c r="AU9" s="117"/>
+      <c r="AV9" s="117"/>
+      <c r="AW9" s="117"/>
+      <c r="AX9" s="117"/>
+      <c r="AY9" s="117"/>
+      <c r="AZ9" s="117"/>
+      <c r="BA9" s="117"/>
+      <c r="BB9" s="117"/>
+      <c r="BC9" s="117"/>
+      <c r="BD9" s="117"/>
+      <c r="BE9" s="117"/>
+      <c r="BF9" s="117"/>
+      <c r="BG9" s="117"/>
+      <c r="BH9" s="117"/>
+      <c r="BI9" s="117"/>
+      <c r="BJ9" s="117"/>
+      <c r="BK9" s="117"/>
+      <c r="BL9" s="117"/>
+      <c r="BM9" s="117"/>
+      <c r="BN9" s="117"/>
+      <c r="BO9" s="117"/>
+      <c r="BP9" s="117"/>
+      <c r="BQ9" s="117"/>
+      <c r="BR9" s="117"/>
+      <c r="BS9" s="117"/>
+      <c r="BT9" s="117"/>
+      <c r="BU9" s="117"/>
+      <c r="BV9" s="117"/>
+      <c r="BW9" s="117"/>
+      <c r="BX9" s="117"/>
+      <c r="BY9" s="117"/>
+      <c r="BZ9" s="117"/>
+      <c r="CA9" s="117"/>
     </row>
     <row r="10" spans="1:79">
-      <c r="E10" s="39"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="39"/>
-      <c r="O10" s="40"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
-      <c r="AN10" s="37"/>
-      <c r="AO10" s="37"/>
-      <c r="AP10" s="37"/>
-      <c r="AR10" s="63"/>
-      <c r="AS10" s="63"/>
-      <c r="AT10" s="63"/>
-      <c r="AU10" s="63"/>
-      <c r="AV10" s="63"/>
-      <c r="AW10" s="63"/>
-      <c r="AX10" s="63"/>
-      <c r="AY10" s="63"/>
-      <c r="AZ10" s="63"/>
-      <c r="BA10" s="63"/>
-      <c r="BB10" s="63"/>
-      <c r="BC10" s="63"/>
-      <c r="BD10" s="63"/>
-      <c r="BE10" s="63"/>
-      <c r="BF10" s="63"/>
-      <c r="BG10" s="63"/>
-      <c r="BH10" s="63"/>
-      <c r="BI10" s="63"/>
-      <c r="BJ10" s="63"/>
-      <c r="BK10" s="63"/>
-      <c r="BL10" s="63"/>
-      <c r="BM10" s="63"/>
-      <c r="BN10" s="63"/>
-      <c r="BO10" s="63"/>
-      <c r="BP10" s="63"/>
-      <c r="BQ10" s="63"/>
-      <c r="BR10" s="63"/>
-      <c r="BS10" s="63"/>
-      <c r="BT10" s="63"/>
-      <c r="BU10" s="63"/>
-      <c r="BV10" s="63"/>
-      <c r="BW10" s="63"/>
-      <c r="BX10" s="63"/>
-      <c r="BY10" s="63"/>
-      <c r="BZ10" s="63"/>
-      <c r="CA10" s="63"/>
+      <c r="E10" s="38"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="38"/>
+      <c r="O10" s="39"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="36"/>
+      <c r="AN10" s="36"/>
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="36"/>
+      <c r="AR10" s="62"/>
+      <c r="AS10" s="62"/>
+      <c r="AT10" s="62"/>
+      <c r="AU10" s="62"/>
+      <c r="AV10" s="62"/>
+      <c r="AW10" s="62"/>
+      <c r="AX10" s="62"/>
+      <c r="AY10" s="62"/>
+      <c r="AZ10" s="62"/>
+      <c r="BA10" s="62"/>
+      <c r="BB10" s="62"/>
+      <c r="BC10" s="62"/>
+      <c r="BD10" s="62"/>
+      <c r="BE10" s="62"/>
+      <c r="BF10" s="62"/>
+      <c r="BG10" s="62"/>
+      <c r="BH10" s="62"/>
+      <c r="BI10" s="62"/>
+      <c r="BJ10" s="62"/>
+      <c r="BK10" s="62"/>
+      <c r="BL10" s="62"/>
+      <c r="BM10" s="62"/>
+      <c r="BN10" s="62"/>
+      <c r="BO10" s="62"/>
+      <c r="BP10" s="62"/>
+      <c r="BQ10" s="62"/>
+      <c r="BR10" s="62"/>
+      <c r="BS10" s="62"/>
+      <c r="BT10" s="62"/>
+      <c r="BU10" s="62"/>
+      <c r="BV10" s="62"/>
+      <c r="BW10" s="62"/>
+      <c r="BX10" s="62"/>
+      <c r="BY10" s="62"/>
+      <c r="BZ10" s="62"/>
+      <c r="CA10" s="62"/>
     </row>
     <row r="11" spans="1:79">
-      <c r="E11" s="39"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="39"/>
-      <c r="O11" s="40"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="37"/>
-      <c r="AR11" s="34" t="s">
+      <c r="E11" s="38"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="38"/>
+      <c r="O11" s="39"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="36"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="36"/>
+      <c r="AN11" s="36"/>
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="36"/>
+      <c r="AR11" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AW11" s="119"/>
-      <c r="AX11" s="119"/>
-      <c r="AY11" s="119"/>
-      <c r="AZ11" s="119"/>
-      <c r="BA11" s="84"/>
-      <c r="BJ11" s="34" t="s">
+      <c r="AW11" s="123"/>
+      <c r="AX11" s="123"/>
+      <c r="AY11" s="123"/>
+      <c r="AZ11" s="123"/>
+      <c r="BA11" s="123"/>
+      <c r="BB11" s="123"/>
+      <c r="BC11" s="123"/>
+      <c r="BD11" s="123"/>
+      <c r="BE11" s="123"/>
+      <c r="BF11" s="123"/>
+      <c r="BJ11" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="BO11" s="119"/>
-      <c r="BP11" s="119"/>
-      <c r="BQ11" s="119"/>
-      <c r="BR11" s="119"/>
+      <c r="BO11" s="123"/>
+      <c r="BP11" s="123"/>
+      <c r="BQ11" s="123"/>
+      <c r="BR11" s="123"/>
+      <c r="BS11" s="123"/>
+      <c r="BT11" s="123"/>
+      <c r="BU11" s="123"/>
+      <c r="BV11" s="123"/>
+      <c r="BW11" s="123"/>
+      <c r="BX11" s="123"/>
     </row>
     <row r="12" spans="1:79">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="118"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="41"/>
-      <c r="S12" s="34" t="s">
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="40"/>
+      <c r="S12" s="33" t="s">
         <v>4</v>
       </c>
       <c r="X12" s="124"/>
@@ -5270,15 +5329,15 @@
       </c>
       <c r="AV12" s="95"/>
       <c r="AW12" s="95"/>
-      <c r="AX12" s="120" t="s">
+      <c r="AX12" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="AY12" s="121"/>
-      <c r="AZ12" s="20"/>
-      <c r="BA12" s="122" t="s">
+      <c r="AY12" s="120"/>
+      <c r="AZ12" s="89"/>
+      <c r="BA12" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="BB12" s="123"/>
+      <c r="BB12" s="122"/>
       <c r="BC12" s="97" t="s">
         <v>5</v>
       </c>
@@ -5298,15 +5357,15 @@
       </c>
       <c r="BN12" s="98"/>
       <c r="BO12" s="98"/>
-      <c r="BP12" s="120" t="s">
+      <c r="BP12" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="BQ12" s="121"/>
-      <c r="BR12" s="20"/>
-      <c r="BS12" s="122" t="s">
+      <c r="BQ12" s="120"/>
+      <c r="BR12" s="89"/>
+      <c r="BS12" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="BT12" s="123"/>
+      <c r="BT12" s="122"/>
       <c r="BU12" s="98" t="s">
         <v>5</v>
       </c>
@@ -5320,15 +5379,15 @@
       <c r="CA12" s="98"/>
     </row>
     <row r="13" spans="1:79">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="41"/>
-      <c r="S13" s="34" t="s">
+      <c r="F13" s="123"/>
+      <c r="G13" s="123"/>
+      <c r="H13" s="123"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="40"/>
+      <c r="S13" s="33" t="s">
         <v>4</v>
       </c>
       <c r="X13" s="124"/>
@@ -5397,15 +5456,15 @@
       </c>
       <c r="E14" s="95"/>
       <c r="F14" s="95"/>
-      <c r="G14" s="120" t="s">
+      <c r="G14" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="H14" s="121"/>
+      <c r="H14" s="120"/>
       <c r="I14" s="20"/>
-      <c r="J14" s="122" t="s">
+      <c r="J14" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="123"/>
+      <c r="K14" s="122"/>
       <c r="L14" s="97" t="s">
         <v>5</v>
       </c>
@@ -5425,15 +5484,15 @@
       </c>
       <c r="W14" s="98"/>
       <c r="X14" s="98"/>
-      <c r="Y14" s="120" t="s">
+      <c r="Y14" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="Z14" s="121"/>
+      <c r="Z14" s="120"/>
       <c r="AA14" s="20"/>
-      <c r="AB14" s="122" t="s">
+      <c r="AB14" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="AC14" s="123"/>
+      <c r="AC14" s="122"/>
       <c r="AD14" s="98" t="s">
         <v>5</v>
       </c>
@@ -5949,11 +6008,11 @@
       <c r="AH20" s="109"/>
       <c r="AI20" s="110"/>
       <c r="AJ20" s="111"/>
-      <c r="AR20" s="34" t="s">
+      <c r="AR20" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="BK20" s="36"/>
-      <c r="BL20" s="39" t="s">
+      <c r="BK20" s="35"/>
+      <c r="BL20" s="38" t="s">
         <v>132</v>
       </c>
     </row>
@@ -5998,42 +6057,42 @@
       <c r="AH21" s="104"/>
       <c r="AI21" s="101"/>
       <c r="AJ21" s="105"/>
-      <c r="AR21" s="63"/>
-      <c r="AS21" s="63"/>
-      <c r="AT21" s="63"/>
-      <c r="AU21" s="63"/>
-      <c r="AV21" s="63"/>
-      <c r="AW21" s="63"/>
-      <c r="AX21" s="63"/>
-      <c r="AY21" s="63"/>
-      <c r="AZ21" s="63"/>
-      <c r="BA21" s="63"/>
-      <c r="BB21" s="63"/>
-      <c r="BC21" s="63"/>
-      <c r="BD21" s="63"/>
-      <c r="BE21" s="63"/>
-      <c r="BF21" s="63"/>
-      <c r="BG21" s="63"/>
-      <c r="BH21" s="63"/>
-      <c r="BI21" s="63"/>
-      <c r="BJ21" s="63"/>
-      <c r="BK21" s="63"/>
-      <c r="BL21" s="63"/>
-      <c r="BM21" s="63"/>
-      <c r="BN21" s="63"/>
-      <c r="BO21" s="63"/>
-      <c r="BP21" s="63"/>
-      <c r="BQ21" s="63"/>
-      <c r="BR21" s="63"/>
-      <c r="BS21" s="63"/>
-      <c r="BT21" s="63"/>
-      <c r="BU21" s="63"/>
-      <c r="BV21" s="63"/>
-      <c r="BW21" s="63"/>
-      <c r="BX21" s="63"/>
-      <c r="BY21" s="63"/>
-      <c r="BZ21" s="63"/>
-      <c r="CA21" s="63"/>
+      <c r="AR21" s="62"/>
+      <c r="AS21" s="62"/>
+      <c r="AT21" s="62"/>
+      <c r="AU21" s="62"/>
+      <c r="AV21" s="62"/>
+      <c r="AW21" s="62"/>
+      <c r="AX21" s="62"/>
+      <c r="AY21" s="62"/>
+      <c r="AZ21" s="62"/>
+      <c r="BA21" s="62"/>
+      <c r="BB21" s="62"/>
+      <c r="BC21" s="62"/>
+      <c r="BD21" s="62"/>
+      <c r="BE21" s="62"/>
+      <c r="BF21" s="62"/>
+      <c r="BG21" s="62"/>
+      <c r="BH21" s="62"/>
+      <c r="BI21" s="62"/>
+      <c r="BJ21" s="62"/>
+      <c r="BK21" s="62"/>
+      <c r="BL21" s="62"/>
+      <c r="BM21" s="62"/>
+      <c r="BN21" s="62"/>
+      <c r="BO21" s="62"/>
+      <c r="BP21" s="62"/>
+      <c r="BQ21" s="62"/>
+      <c r="BR21" s="62"/>
+      <c r="BS21" s="62"/>
+      <c r="BT21" s="62"/>
+      <c r="BU21" s="62"/>
+      <c r="BV21" s="62"/>
+      <c r="BW21" s="62"/>
+      <c r="BX21" s="62"/>
+      <c r="BY21" s="62"/>
+      <c r="BZ21" s="62"/>
+      <c r="CA21" s="62"/>
     </row>
     <row r="22" spans="1:79">
       <c r="A22" s="104"/>
@@ -6088,21 +6147,32 @@
       </c>
       <c r="AI22" s="98"/>
       <c r="AJ22" s="98"/>
-      <c r="AR22" s="34" t="s">
+      <c r="AR22" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="AW22" s="118"/>
-      <c r="AX22" s="118"/>
-      <c r="AY22" s="118"/>
-      <c r="AZ22" s="118"/>
-      <c r="BA22" s="41"/>
-      <c r="BJ22" s="34" t="s">
+      <c r="AW22" s="123"/>
+      <c r="AX22" s="123"/>
+      <c r="AY22" s="123"/>
+      <c r="AZ22" s="123"/>
+      <c r="BA22" s="123"/>
+      <c r="BB22" s="123"/>
+      <c r="BC22" s="123"/>
+      <c r="BD22" s="123"/>
+      <c r="BE22" s="123"/>
+      <c r="BF22" s="123"/>
+      <c r="BJ22" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="BO22" s="119"/>
-      <c r="BP22" s="119"/>
-      <c r="BQ22" s="119"/>
-      <c r="BR22" s="119"/>
+      <c r="BO22" s="123"/>
+      <c r="BP22" s="123"/>
+      <c r="BQ22" s="123"/>
+      <c r="BR22" s="123"/>
+      <c r="BS22" s="123"/>
+      <c r="BT22" s="123"/>
+      <c r="BU22" s="123"/>
+      <c r="BV22" s="123"/>
+      <c r="BW22" s="123"/>
+      <c r="BX22" s="123"/>
     </row>
     <row r="23" spans="1:79">
       <c r="A23" s="97" t="s">
@@ -6153,15 +6223,15 @@
       </c>
       <c r="AV23" s="95"/>
       <c r="AW23" s="95"/>
-      <c r="AX23" s="120" t="s">
+      <c r="AX23" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="AY23" s="121"/>
-      <c r="AZ23" s="20"/>
-      <c r="BA23" s="122" t="s">
+      <c r="AY23" s="120"/>
+      <c r="AZ23" s="89"/>
+      <c r="BA23" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="BB23" s="123"/>
+      <c r="BB23" s="122"/>
       <c r="BC23" s="97" t="s">
         <v>5</v>
       </c>
@@ -6181,15 +6251,15 @@
       </c>
       <c r="BN23" s="98"/>
       <c r="BO23" s="98"/>
-      <c r="BP23" s="120" t="s">
+      <c r="BP23" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="BQ23" s="121"/>
-      <c r="BR23" s="20"/>
-      <c r="BS23" s="122" t="s">
+      <c r="BQ23" s="120"/>
+      <c r="BR23" s="89"/>
+      <c r="BS23" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="BT23" s="123"/>
+      <c r="BT23" s="122"/>
       <c r="BU23" s="98" t="s">
         <v>5</v>
       </c>
@@ -6625,11 +6695,11 @@
       <c r="CA28" s="108"/>
     </row>
     <row r="29" spans="1:79">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="T29" s="36"/>
-      <c r="U29" s="39" t="s">
+      <c r="T29" s="35"/>
+      <c r="U29" s="38" t="s">
         <v>132</v>
       </c>
       <c r="AR29" s="97" t="s">
@@ -6676,7 +6746,7 @@
     <row r="30" spans="1:79">
       <c r="A30" s="100"/>
       <c r="B30" s="100"/>
-      <c r="C30" s="34" t="s">
+      <c r="C30" s="33" t="s">
         <v>91</v>
       </c>
       <c r="AR30" s="97" t="s">
@@ -6730,21 +6800,21 @@
       <c r="G31" s="100"/>
       <c r="H31" s="100"/>
       <c r="I31" s="100"/>
-      <c r="AR31" s="34" t="s">
+      <c r="AR31" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="BK31" s="36"/>
-      <c r="BL31" s="39" t="s">
+      <c r="BK31" s="35"/>
+      <c r="BL31" s="38" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:79">
-      <c r="A32" s="34" t="s">
+      <c r="A32" s="33" t="s">
         <v>96</v>
       </c>
       <c r="G32" s="102"/>
       <c r="H32" s="102"/>
-      <c r="I32" s="34" t="s">
+      <c r="I32" s="33" t="s">
         <v>97</v>
       </c>
       <c r="K32" s="100"/>
@@ -6752,10 +6822,10 @@
       <c r="M32" s="100"/>
       <c r="N32" s="100"/>
       <c r="O32" s="100"/>
-      <c r="P32" s="34" t="s">
+      <c r="P32" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AR32" s="34" t="s">
+      <c r="AR32" s="33" t="s">
         <v>6</v>
       </c>
     </row>
@@ -6771,17 +6841,17 @@
       <c r="I33" s="100"/>
     </row>
     <row r="34" spans="1:42">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="33" t="s">
         <v>82</v>
       </c>
       <c r="H34" s="100"/>
       <c r="I34" s="100"/>
-      <c r="J34" s="34" t="s">
+      <c r="J34" s="33" t="s">
         <v>99</v>
       </c>
       <c r="R34" s="100"/>
       <c r="S34" s="100"/>
-      <c r="T34" s="34" t="s">
+      <c r="T34" s="33" t="s">
         <v>100</v>
       </c>
     </row>
@@ -6790,7 +6860,7 @@
       <c r="B35" s="100"/>
       <c r="C35" s="100"/>
       <c r="D35" s="100"/>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="33" t="s">
         <v>101</v>
       </c>
       <c r="H35" s="100"/>
@@ -6798,17 +6868,17 @@
       <c r="J35" s="100"/>
       <c r="K35" s="100"/>
       <c r="L35" s="100"/>
-      <c r="M35" s="34" t="s">
+      <c r="M35" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AK35" s="43"/>
-      <c r="AL35" s="44"/>
-      <c r="AM35" s="43" t="s">
+      <c r="AK35" s="42"/>
+      <c r="AL35" s="43"/>
+      <c r="AM35" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="AN35" s="43"/>
-      <c r="AO35" s="43"/>
-      <c r="AP35" s="44"/>
+      <c r="AN35" s="42"/>
+      <c r="AO35" s="42"/>
+      <c r="AP35" s="43"/>
     </row>
     <row r="36" spans="1:42">
       <c r="A36" s="100"/>
@@ -6820,22 +6890,22 @@
       <c r="G36" s="100"/>
       <c r="H36" s="100"/>
       <c r="I36" s="100"/>
-      <c r="AK36" s="43"/>
-      <c r="AL36" s="44"/>
-      <c r="AM36" s="44" t="s">
+      <c r="AK36" s="42"/>
+      <c r="AL36" s="43"/>
+      <c r="AM36" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AN36" s="43"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="44"/>
+      <c r="AN36" s="42"/>
+      <c r="AO36" s="42"/>
+      <c r="AP36" s="43"/>
     </row>
     <row r="37" spans="1:42">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="33" t="s">
         <v>102</v>
       </c>
       <c r="L37" s="100"/>
       <c r="M37" s="100"/>
-      <c r="N37" s="34" t="s">
+      <c r="N37" s="33" t="s">
         <v>103</v>
       </c>
       <c r="P37" s="100"/>
@@ -6844,46 +6914,46 @@
       <c r="S37" s="100"/>
       <c r="T37" s="100"/>
       <c r="U37" s="100"/>
-      <c r="V37" s="34" t="s">
+      <c r="V37" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="AK37" s="82"/>
-      <c r="AL37" s="80"/>
+      <c r="AK37" s="81"/>
+      <c r="AL37" s="79"/>
       <c r="AM37" s="106"/>
       <c r="AN37" s="107"/>
       <c r="AO37" s="107"/>
       <c r="AP37" s="108"/>
     </row>
     <row r="38" spans="1:42">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="33" t="s">
         <v>92</v>
       </c>
       <c r="E38" s="100"/>
       <c r="F38" s="100"/>
-      <c r="G38" s="34" t="s">
+      <c r="G38" s="33" t="s">
         <v>99</v>
       </c>
       <c r="O38" s="100"/>
       <c r="P38" s="100"/>
-      <c r="Q38" s="34" t="s">
+      <c r="Q38" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="AK38" s="82"/>
-      <c r="AL38" s="80"/>
+      <c r="AK38" s="81"/>
+      <c r="AL38" s="79"/>
       <c r="AM38" s="109"/>
       <c r="AN38" s="110"/>
       <c r="AO38" s="110"/>
       <c r="AP38" s="111"/>
     </row>
     <row r="39" spans="1:42">
-      <c r="A39" s="34" t="s">
+      <c r="A39" s="33" t="s">
         <v>106</v>
       </c>
       <c r="F39" s="100"/>
       <c r="G39" s="100"/>
       <c r="H39" s="100"/>
       <c r="I39" s="100"/>
-      <c r="J39" s="34" t="s">
+      <c r="J39" s="33" t="s">
         <v>101</v>
       </c>
       <c r="M39" s="100"/>
@@ -6891,147 +6961,147 @@
       <c r="O39" s="100"/>
       <c r="P39" s="100"/>
       <c r="Q39" s="100"/>
-      <c r="R39" s="34" t="s">
+      <c r="R39" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AK39" s="82"/>
-      <c r="AL39" s="80"/>
+      <c r="AK39" s="81"/>
+      <c r="AL39" s="79"/>
       <c r="AM39" s="109"/>
       <c r="AN39" s="110"/>
       <c r="AO39" s="110"/>
       <c r="AP39" s="111"/>
     </row>
     <row r="40" spans="1:42">
-      <c r="AK40" s="82"/>
-      <c r="AL40" s="80"/>
+      <c r="AK40" s="81"/>
+      <c r="AL40" s="79"/>
       <c r="AM40" s="106"/>
       <c r="AN40" s="107"/>
       <c r="AO40" s="107"/>
       <c r="AP40" s="108"/>
     </row>
     <row r="41" spans="1:42" ht="15" customHeight="1">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="33" t="s">
         <v>107</v>
       </c>
       <c r="K41" s="100"/>
       <c r="L41" s="100"/>
-      <c r="M41" s="34" t="s">
+      <c r="M41" s="33" t="s">
         <v>108</v>
       </c>
       <c r="Q41" s="100"/>
       <c r="R41" s="100"/>
-      <c r="S41" s="34" t="s">
+      <c r="S41" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="AK41" s="82"/>
-      <c r="AL41" s="80"/>
+      <c r="AK41" s="81"/>
+      <c r="AL41" s="79"/>
       <c r="AM41" s="109"/>
       <c r="AN41" s="110"/>
       <c r="AO41" s="110"/>
       <c r="AP41" s="111"/>
     </row>
     <row r="42" spans="1:42" ht="15" customHeight="1">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="AK42" s="82"/>
-      <c r="AL42" s="80"/>
+      <c r="AK42" s="81"/>
+      <c r="AL42" s="79"/>
       <c r="AM42" s="104"/>
       <c r="AN42" s="101"/>
       <c r="AO42" s="101"/>
       <c r="AP42" s="105"/>
     </row>
     <row r="43" spans="1:42" ht="15" customHeight="1">
-      <c r="A43" s="34" t="s">
+      <c r="A43" s="33" t="s">
         <v>111</v>
       </c>
       <c r="E43" s="100"/>
       <c r="F43" s="100"/>
       <c r="G43" s="100"/>
       <c r="H43" s="100"/>
-      <c r="I43" s="34" t="s">
+      <c r="I43" s="33" t="s">
         <v>112</v>
       </c>
       <c r="K43" s="100"/>
       <c r="L43" s="100"/>
-      <c r="M43" s="34" t="s">
+      <c r="M43" s="33" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:42" ht="15" customHeight="1"/>
     <row r="45" spans="1:42" ht="15" customHeight="1">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="33" t="s">
         <v>113</v>
       </c>
       <c r="M45" s="100"/>
       <c r="N45" s="100"/>
-      <c r="O45" s="34" t="s">
+      <c r="O45" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="AK45" s="43"/>
-      <c r="AL45" s="44"/>
-      <c r="AM45" s="43" t="s">
+      <c r="AK45" s="42"/>
+      <c r="AL45" s="43"/>
+      <c r="AM45" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="AN45" s="43"/>
-      <c r="AO45" s="43"/>
-      <c r="AP45" s="44"/>
+      <c r="AN45" s="42"/>
+      <c r="AO45" s="42"/>
+      <c r="AP45" s="43"/>
     </row>
     <row r="46" spans="1:42" ht="15" customHeight="1">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="33" t="s">
         <v>115</v>
       </c>
       <c r="X46" s="100"/>
       <c r="Y46" s="100"/>
       <c r="Z46" s="100"/>
       <c r="AA46" s="100"/>
-      <c r="AB46" s="34" t="s">
+      <c r="AB46" s="33" t="s">
         <v>112</v>
       </c>
       <c r="AD46" s="100"/>
       <c r="AE46" s="100"/>
-      <c r="AF46" s="34" t="s">
+      <c r="AF46" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="AK46" s="43"/>
-      <c r="AL46" s="44"/>
-      <c r="AM46" s="44" t="s">
+      <c r="AK46" s="42"/>
+      <c r="AL46" s="43"/>
+      <c r="AM46" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AN46" s="43"/>
-      <c r="AO46" s="43"/>
-      <c r="AP46" s="44"/>
+      <c r="AN46" s="42"/>
+      <c r="AO46" s="42"/>
+      <c r="AP46" s="43"/>
     </row>
     <row r="47" spans="1:42" ht="15" customHeight="1">
       <c r="A47" s="100"/>
       <c r="B47" s="100"/>
       <c r="C47" s="100"/>
       <c r="D47" s="100"/>
-      <c r="E47" s="34" t="s">
+      <c r="E47" s="33" t="s">
         <v>112</v>
       </c>
       <c r="G47" s="100"/>
       <c r="H47" s="100"/>
-      <c r="I47" s="34" t="s">
+      <c r="I47" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="AK47" s="82"/>
-      <c r="AL47" s="80"/>
+      <c r="AK47" s="81"/>
+      <c r="AL47" s="79"/>
       <c r="AM47" s="106"/>
       <c r="AN47" s="107"/>
       <c r="AO47" s="107"/>
       <c r="AP47" s="108"/>
     </row>
     <row r="48" spans="1:42" ht="15" customHeight="1">
-      <c r="AK48" s="82"/>
-      <c r="AL48" s="80"/>
+      <c r="AK48" s="81"/>
+      <c r="AL48" s="79"/>
       <c r="AM48" s="109"/>
       <c r="AN48" s="110"/>
       <c r="AO48" s="110"/>
       <c r="AP48" s="111"/>
     </row>
     <row r="49" spans="1:42" ht="15" customHeight="1">
-      <c r="A49" s="34" t="s">
+      <c r="A49" s="33" t="s">
         <v>117</v>
       </c>
       <c r="K49" s="100"/>
@@ -7048,15 +7118,15 @@
       <c r="V49" s="100"/>
       <c r="W49" s="100"/>
       <c r="X49" s="100"/>
-      <c r="AK49" s="82"/>
-      <c r="AL49" s="80"/>
+      <c r="AK49" s="81"/>
+      <c r="AL49" s="79"/>
       <c r="AM49" s="109"/>
       <c r="AN49" s="110"/>
       <c r="AO49" s="110"/>
       <c r="AP49" s="111"/>
     </row>
     <row r="50" spans="1:42" ht="15" customHeight="1">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="33" t="s">
         <v>41</v>
       </c>
       <c r="G50" s="100"/>
@@ -7073,155 +7143,155 @@
       <c r="S50" s="100"/>
       <c r="T50" s="100"/>
       <c r="U50" s="100"/>
-      <c r="V50" s="34" t="s">
+      <c r="V50" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="AK50" s="82"/>
-      <c r="AL50" s="80"/>
+      <c r="AK50" s="81"/>
+      <c r="AL50" s="79"/>
       <c r="AM50" s="106"/>
       <c r="AN50" s="107"/>
       <c r="AO50" s="107"/>
       <c r="AP50" s="108"/>
     </row>
     <row r="51" spans="1:42" ht="15" customHeight="1">
-      <c r="AK51" s="82"/>
-      <c r="AL51" s="80"/>
+      <c r="AK51" s="81"/>
+      <c r="AL51" s="79"/>
       <c r="AM51" s="109"/>
       <c r="AN51" s="110"/>
       <c r="AO51" s="110"/>
       <c r="AP51" s="111"/>
     </row>
     <row r="52" spans="1:42" ht="15" customHeight="1">
-      <c r="AK52" s="82"/>
-      <c r="AL52" s="80"/>
+      <c r="AK52" s="81"/>
+      <c r="AL52" s="79"/>
       <c r="AM52" s="104"/>
       <c r="AN52" s="101"/>
       <c r="AO52" s="101"/>
       <c r="AP52" s="105"/>
     </row>
     <row r="53" spans="1:42">
-      <c r="A53" s="34" t="s">
+      <c r="A53" s="33" t="s">
         <v>4</v>
       </c>
       <c r="G53" s="103"/>
       <c r="H53" s="103"/>
       <c r="I53" s="103"/>
-      <c r="W53" s="34" t="s">
+      <c r="W53" s="33" t="s">
         <v>4</v>
       </c>
       <c r="AC53" s="103"/>
       <c r="AD53" s="103"/>
       <c r="AE53" s="103"/>
-      <c r="AK53" s="82"/>
-      <c r="AL53" s="82"/>
-      <c r="AM53" s="82"/>
-      <c r="AN53" s="82"/>
-      <c r="AO53" s="82"/>
-      <c r="AP53" s="80"/>
+      <c r="AK53" s="81"/>
+      <c r="AL53" s="81"/>
+      <c r="AM53" s="81"/>
+      <c r="AN53" s="81"/>
+      <c r="AO53" s="81"/>
+      <c r="AP53" s="79"/>
     </row>
     <row r="54" spans="1:42">
       <c r="A54" s="97"/>
       <c r="B54" s="95"/>
       <c r="C54" s="96"/>
-      <c r="D54" s="42" t="s">
+      <c r="D54" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="43"/>
-      <c r="I54" s="42" t="s">
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="J54" s="43"/>
-      <c r="K54" s="43"/>
-      <c r="L54" s="43"/>
-      <c r="M54" s="44"/>
-      <c r="N54" s="43" t="s">
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="43"/>
+      <c r="N54" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="O54" s="43"/>
-      <c r="P54" s="43"/>
-      <c r="Q54" s="43"/>
-      <c r="R54" s="44"/>
-      <c r="S54" s="43" t="s">
+      <c r="O54" s="42"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="42"/>
+      <c r="R54" s="43"/>
+      <c r="S54" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="T54" s="43"/>
-      <c r="U54" s="43"/>
-      <c r="V54" s="43"/>
-      <c r="W54" s="44"/>
-      <c r="X54" s="43" t="s">
+      <c r="T54" s="42"/>
+      <c r="U54" s="42"/>
+      <c r="V54" s="42"/>
+      <c r="W54" s="43"/>
+      <c r="X54" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="Y54" s="43"/>
-      <c r="Z54" s="43"/>
-      <c r="AA54" s="43"/>
-      <c r="AB54" s="44"/>
-      <c r="AC54" s="43" t="s">
+      <c r="Y54" s="42"/>
+      <c r="Z54" s="42"/>
+      <c r="AA54" s="42"/>
+      <c r="AB54" s="43"/>
+      <c r="AC54" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="AD54" s="43"/>
-      <c r="AE54" s="43"/>
-      <c r="AF54" s="43"/>
-      <c r="AG54" s="44"/>
-      <c r="AH54" s="43" t="s">
+      <c r="AD54" s="42"/>
+      <c r="AE54" s="42"/>
+      <c r="AF54" s="42"/>
+      <c r="AG54" s="43"/>
+      <c r="AH54" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AI54" s="43"/>
-      <c r="AJ54" s="43"/>
+      <c r="AI54" s="42"/>
+      <c r="AJ54" s="42"/>
     </row>
     <row r="55" spans="1:42">
       <c r="A55" s="104"/>
       <c r="B55" s="101"/>
       <c r="C55" s="105"/>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="45" t="s">
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="J55" s="43"/>
-      <c r="K55" s="43"/>
-      <c r="L55" s="43"/>
-      <c r="M55" s="44"/>
-      <c r="N55" s="43" t="s">
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="43"/>
+      <c r="N55" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="O55" s="43"/>
-      <c r="P55" s="43"/>
-      <c r="Q55" s="43"/>
-      <c r="R55" s="44"/>
-      <c r="S55" s="43" t="s">
+      <c r="O55" s="42"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="42"/>
+      <c r="R55" s="43"/>
+      <c r="S55" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="T55" s="43"/>
-      <c r="U55" s="43"/>
-      <c r="V55" s="43"/>
-      <c r="W55" s="44"/>
-      <c r="X55" s="44" t="s">
+      <c r="T55" s="42"/>
+      <c r="U55" s="42"/>
+      <c r="V55" s="42"/>
+      <c r="W55" s="43"/>
+      <c r="X55" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="Y55" s="43"/>
-      <c r="Z55" s="43"/>
-      <c r="AA55" s="43"/>
-      <c r="AB55" s="44"/>
-      <c r="AC55" s="44" t="s">
+      <c r="Y55" s="42"/>
+      <c r="Z55" s="42"/>
+      <c r="AA55" s="42"/>
+      <c r="AB55" s="43"/>
+      <c r="AC55" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="AD55" s="43"/>
-      <c r="AE55" s="43"/>
-      <c r="AF55" s="43"/>
-      <c r="AG55" s="44"/>
-      <c r="AH55" s="44" t="s">
+      <c r="AD55" s="42"/>
+      <c r="AE55" s="42"/>
+      <c r="AF55" s="42"/>
+      <c r="AG55" s="43"/>
+      <c r="AH55" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AI55" s="43"/>
-      <c r="AJ55" s="43"/>
+      <c r="AI55" s="42"/>
+      <c r="AJ55" s="42"/>
     </row>
     <row r="56" spans="1:42">
       <c r="A56" s="106" t="s">
@@ -7259,9 +7329,9 @@
       <c r="AE56" s="95"/>
       <c r="AF56" s="95"/>
       <c r="AG56" s="96"/>
-      <c r="AH56" s="81"/>
-      <c r="AI56" s="82"/>
-      <c r="AJ56" s="82"/>
+      <c r="AH56" s="80"/>
+      <c r="AI56" s="81"/>
+      <c r="AJ56" s="81"/>
     </row>
     <row r="57" spans="1:42">
       <c r="A57" s="109" t="s">
@@ -7299,9 +7369,9 @@
       <c r="AE57" s="95"/>
       <c r="AF57" s="95"/>
       <c r="AG57" s="96"/>
-      <c r="AH57" s="81"/>
-      <c r="AI57" s="82"/>
-      <c r="AJ57" s="82"/>
+      <c r="AH57" s="80"/>
+      <c r="AI57" s="81"/>
+      <c r="AJ57" s="81"/>
     </row>
     <row r="58" spans="1:42">
       <c r="A58" s="109" t="s">
@@ -7339,9 +7409,9 @@
       <c r="AE58" s="95"/>
       <c r="AF58" s="95"/>
       <c r="AG58" s="96"/>
-      <c r="AH58" s="81"/>
-      <c r="AI58" s="82"/>
-      <c r="AJ58" s="82"/>
+      <c r="AH58" s="80"/>
+      <c r="AI58" s="81"/>
+      <c r="AJ58" s="81"/>
     </row>
     <row r="59" spans="1:42">
       <c r="A59" s="109" t="s">
@@ -7379,9 +7449,9 @@
       <c r="AE59" s="95"/>
       <c r="AF59" s="95"/>
       <c r="AG59" s="96"/>
-      <c r="AH59" s="81"/>
-      <c r="AI59" s="82"/>
-      <c r="AJ59" s="82"/>
+      <c r="AH59" s="80"/>
+      <c r="AI59" s="81"/>
+      <c r="AJ59" s="81"/>
     </row>
     <row r="60" spans="1:42">
       <c r="A60" s="109" t="s">
@@ -7419,9 +7489,9 @@
       <c r="AE60" s="95"/>
       <c r="AF60" s="95"/>
       <c r="AG60" s="96"/>
-      <c r="AH60" s="81"/>
-      <c r="AI60" s="82"/>
-      <c r="AJ60" s="82"/>
+      <c r="AH60" s="80"/>
+      <c r="AI60" s="81"/>
+      <c r="AJ60" s="81"/>
     </row>
     <row r="61" spans="1:42">
       <c r="A61" s="104" t="s">
@@ -7459,21 +7529,21 @@
       <c r="AE61" s="95"/>
       <c r="AF61" s="95"/>
       <c r="AG61" s="96"/>
-      <c r="AH61" s="81"/>
-      <c r="AI61" s="82"/>
-      <c r="AJ61" s="82"/>
+      <c r="AH61" s="80"/>
+      <c r="AI61" s="81"/>
+      <c r="AJ61" s="81"/>
     </row>
     <row r="62" spans="1:42">
-      <c r="A62" s="52"/>
+      <c r="A62" s="51"/>
     </row>
     <row r="63" spans="1:42">
-      <c r="A63" s="34" t="s">
+      <c r="A63" s="33" t="s">
         <v>4</v>
       </c>
       <c r="G63" s="103"/>
       <c r="H63" s="103"/>
       <c r="I63" s="103"/>
-      <c r="W63" s="34" t="s">
+      <c r="W63" s="33" t="s">
         <v>4</v>
       </c>
       <c r="AC63" s="103"/>
@@ -7484,105 +7554,105 @@
       <c r="A64" s="97"/>
       <c r="B64" s="95"/>
       <c r="C64" s="96"/>
-      <c r="D64" s="42" t="s">
+      <c r="D64" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="G64" s="43"/>
-      <c r="H64" s="43"/>
-      <c r="I64" s="42" t="s">
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="J64" s="43"/>
-      <c r="K64" s="43"/>
-      <c r="L64" s="43"/>
-      <c r="M64" s="44"/>
-      <c r="N64" s="43" t="s">
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
+      <c r="L64" s="42"/>
+      <c r="M64" s="43"/>
+      <c r="N64" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="O64" s="43"/>
-      <c r="P64" s="43"/>
-      <c r="Q64" s="43"/>
-      <c r="R64" s="44"/>
-      <c r="S64" s="43" t="s">
+      <c r="O64" s="42"/>
+      <c r="P64" s="42"/>
+      <c r="Q64" s="42"/>
+      <c r="R64" s="43"/>
+      <c r="S64" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="T64" s="43"/>
-      <c r="U64" s="43"/>
-      <c r="V64" s="43"/>
-      <c r="W64" s="44"/>
-      <c r="X64" s="43" t="s">
+      <c r="T64" s="42"/>
+      <c r="U64" s="42"/>
+      <c r="V64" s="42"/>
+      <c r="W64" s="43"/>
+      <c r="X64" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="Y64" s="43"/>
-      <c r="Z64" s="43"/>
-      <c r="AA64" s="43"/>
-      <c r="AB64" s="44"/>
-      <c r="AC64" s="43" t="s">
+      <c r="Y64" s="42"/>
+      <c r="Z64" s="42"/>
+      <c r="AA64" s="42"/>
+      <c r="AB64" s="43"/>
+      <c r="AC64" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="AD64" s="43"/>
-      <c r="AE64" s="43"/>
-      <c r="AF64" s="43"/>
-      <c r="AG64" s="44"/>
-      <c r="AH64" s="43" t="s">
+      <c r="AD64" s="42"/>
+      <c r="AE64" s="42"/>
+      <c r="AF64" s="42"/>
+      <c r="AG64" s="43"/>
+      <c r="AH64" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="AI64" s="43"/>
-      <c r="AJ64" s="43"/>
+      <c r="AI64" s="42"/>
+      <c r="AJ64" s="42"/>
     </row>
     <row r="65" spans="1:36">
       <c r="A65" s="104"/>
       <c r="B65" s="101"/>
       <c r="C65" s="105"/>
-      <c r="D65" s="45" t="s">
+      <c r="D65" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="41"/>
-      <c r="H65" s="41"/>
-      <c r="I65" s="45" t="s">
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="J65" s="43"/>
-      <c r="K65" s="43"/>
-      <c r="L65" s="43"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="43" t="s">
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
+      <c r="L65" s="42"/>
+      <c r="M65" s="43"/>
+      <c r="N65" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="O65" s="43"/>
-      <c r="P65" s="43"/>
-      <c r="Q65" s="43"/>
-      <c r="R65" s="44"/>
-      <c r="S65" s="43" t="s">
+      <c r="O65" s="42"/>
+      <c r="P65" s="42"/>
+      <c r="Q65" s="42"/>
+      <c r="R65" s="43"/>
+      <c r="S65" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="T65" s="43"/>
-      <c r="U65" s="43"/>
-      <c r="V65" s="43"/>
-      <c r="W65" s="44"/>
-      <c r="X65" s="44" t="s">
+      <c r="T65" s="42"/>
+      <c r="U65" s="42"/>
+      <c r="V65" s="42"/>
+      <c r="W65" s="43"/>
+      <c r="X65" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="Y65" s="43"/>
-      <c r="Z65" s="43"/>
-      <c r="AA65" s="43"/>
-      <c r="AB65" s="44"/>
-      <c r="AC65" s="44" t="s">
+      <c r="Y65" s="42"/>
+      <c r="Z65" s="42"/>
+      <c r="AA65" s="42"/>
+      <c r="AB65" s="43"/>
+      <c r="AC65" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="AD65" s="43"/>
-      <c r="AE65" s="43"/>
-      <c r="AF65" s="43"/>
-      <c r="AG65" s="44"/>
-      <c r="AH65" s="44" t="s">
+      <c r="AD65" s="42"/>
+      <c r="AE65" s="42"/>
+      <c r="AF65" s="42"/>
+      <c r="AG65" s="43"/>
+      <c r="AH65" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="AI65" s="43"/>
-      <c r="AJ65" s="43"/>
+      <c r="AI65" s="42"/>
+      <c r="AJ65" s="42"/>
     </row>
     <row r="66" spans="1:36">
       <c r="A66" s="106" t="s">
@@ -7620,9 +7690,9 @@
       <c r="AE66" s="95"/>
       <c r="AF66" s="95"/>
       <c r="AG66" s="96"/>
-      <c r="AH66" s="81"/>
-      <c r="AI66" s="82"/>
-      <c r="AJ66" s="82"/>
+      <c r="AH66" s="80"/>
+      <c r="AI66" s="81"/>
+      <c r="AJ66" s="81"/>
     </row>
     <row r="67" spans="1:36">
       <c r="A67" s="109" t="s">
@@ -7660,9 +7730,9 @@
       <c r="AE67" s="95"/>
       <c r="AF67" s="95"/>
       <c r="AG67" s="96"/>
-      <c r="AH67" s="81"/>
-      <c r="AI67" s="82"/>
-      <c r="AJ67" s="82"/>
+      <c r="AH67" s="80"/>
+      <c r="AI67" s="81"/>
+      <c r="AJ67" s="81"/>
     </row>
     <row r="68" spans="1:36">
       <c r="A68" s="109" t="s">
@@ -7700,9 +7770,9 @@
       <c r="AE68" s="95"/>
       <c r="AF68" s="95"/>
       <c r="AG68" s="96"/>
-      <c r="AH68" s="81"/>
-      <c r="AI68" s="82"/>
-      <c r="AJ68" s="82"/>
+      <c r="AH68" s="80"/>
+      <c r="AI68" s="81"/>
+      <c r="AJ68" s="81"/>
     </row>
     <row r="69" spans="1:36">
       <c r="A69" s="109" t="s">
@@ -7740,9 +7810,9 @@
       <c r="AE69" s="95"/>
       <c r="AF69" s="95"/>
       <c r="AG69" s="96"/>
-      <c r="AH69" s="81"/>
-      <c r="AI69" s="82"/>
-      <c r="AJ69" s="82"/>
+      <c r="AH69" s="80"/>
+      <c r="AI69" s="81"/>
+      <c r="AJ69" s="81"/>
     </row>
     <row r="70" spans="1:36">
       <c r="A70" s="109" t="s">
@@ -7780,9 +7850,9 @@
       <c r="AE70" s="95"/>
       <c r="AF70" s="95"/>
       <c r="AG70" s="96"/>
-      <c r="AH70" s="81"/>
-      <c r="AI70" s="82"/>
-      <c r="AJ70" s="82"/>
+      <c r="AH70" s="80"/>
+      <c r="AI70" s="81"/>
+      <c r="AJ70" s="81"/>
     </row>
     <row r="71" spans="1:36">
       <c r="A71" s="104" t="s">
@@ -7820,69 +7890,76 @@
       <c r="AE71" s="95"/>
       <c r="AF71" s="95"/>
       <c r="AG71" s="96"/>
-      <c r="AH71" s="81"/>
-      <c r="AI71" s="82"/>
-      <c r="AJ71" s="82"/>
+      <c r="AH71" s="80"/>
+      <c r="AI71" s="81"/>
+      <c r="AJ71" s="81"/>
     </row>
     <row r="72" spans="1:36">
-      <c r="A72" s="81" t="s">
+      <c r="A72" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="B72" s="82"/>
-      <c r="C72" s="82"/>
-      <c r="D72" s="82"/>
-      <c r="E72" s="82"/>
-      <c r="F72" s="82"/>
-      <c r="G72" s="82"/>
-      <c r="H72" s="82"/>
-      <c r="I72" s="82"/>
-      <c r="J72" s="82"/>
-      <c r="K72" s="82"/>
-      <c r="L72" s="82"/>
-      <c r="M72" s="82"/>
-      <c r="N72" s="82"/>
-      <c r="O72" s="82"/>
-      <c r="P72" s="82"/>
-      <c r="Q72" s="82"/>
-      <c r="R72" s="82"/>
-      <c r="S72" s="82"/>
-      <c r="T72" s="82"/>
-      <c r="U72" s="82"/>
-      <c r="V72" s="82"/>
-      <c r="W72" s="82"/>
-      <c r="X72" s="82"/>
-      <c r="Y72" s="82"/>
-      <c r="Z72" s="82"/>
-      <c r="AA72" s="82"/>
-      <c r="AB72" s="82"/>
-      <c r="AC72" s="82"/>
-      <c r="AD72" s="82"/>
-      <c r="AE72" s="82"/>
-      <c r="AF72" s="82"/>
-      <c r="AG72" s="82"/>
-      <c r="AH72" s="82"/>
-      <c r="AI72" s="82"/>
-      <c r="AJ72" s="82"/>
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="81"/>
+      <c r="N72" s="81"/>
+      <c r="O72" s="81"/>
+      <c r="P72" s="81"/>
+      <c r="Q72" s="81"/>
+      <c r="R72" s="81"/>
+      <c r="S72" s="81"/>
+      <c r="T72" s="81"/>
+      <c r="U72" s="81"/>
+      <c r="V72" s="81"/>
+      <c r="W72" s="81"/>
+      <c r="X72" s="81"/>
+      <c r="Y72" s="81"/>
+      <c r="Z72" s="81"/>
+      <c r="AA72" s="81"/>
+      <c r="AB72" s="81"/>
+      <c r="AC72" s="81"/>
+      <c r="AD72" s="81"/>
+      <c r="AE72" s="81"/>
+      <c r="AF72" s="81"/>
+      <c r="AG72" s="81"/>
+      <c r="AH72" s="81"/>
+      <c r="AI72" s="81"/>
+      <c r="AJ72" s="81"/>
     </row>
     <row r="74" spans="1:36">
-      <c r="A74" s="34" t="s">
+      <c r="A74" s="33" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="434">
+  <mergeCells count="435">
+    <mergeCell ref="AW22:BF22"/>
+    <mergeCell ref="BO22:BX22"/>
+    <mergeCell ref="BO11:BX11"/>
+    <mergeCell ref="AW11:BF11"/>
     <mergeCell ref="BP15:BT15"/>
     <mergeCell ref="BU15:BX15"/>
     <mergeCell ref="BP16:BT16"/>
     <mergeCell ref="BU16:BX16"/>
     <mergeCell ref="BU17:BX17"/>
-    <mergeCell ref="AR19:AT19"/>
-    <mergeCell ref="AU19:AW19"/>
-    <mergeCell ref="AX19:BB19"/>
-    <mergeCell ref="BC19:BF19"/>
+    <mergeCell ref="BC15:BF15"/>
+    <mergeCell ref="BJ15:BL15"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BJ14:BL14"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BP14:BT14"/>
     <mergeCell ref="BJ19:BL19"/>
     <mergeCell ref="BM19:BO19"/>
     <mergeCell ref="BP17:BT17"/>
+    <mergeCell ref="BP18:BT18"/>
     <mergeCell ref="AR16:AT16"/>
     <mergeCell ref="AU16:AW16"/>
     <mergeCell ref="AX16:BB16"/>
@@ -7897,7 +7974,6 @@
     <mergeCell ref="BM17:BO17"/>
     <mergeCell ref="BJ18:BL18"/>
     <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="BP18:BT18"/>
     <mergeCell ref="BY17:CA19"/>
     <mergeCell ref="AR18:AT18"/>
     <mergeCell ref="AU18:AW18"/>
@@ -7922,11 +7998,6 @@
     <mergeCell ref="AR15:AT15"/>
     <mergeCell ref="AU15:AW15"/>
     <mergeCell ref="AX15:BB15"/>
-    <mergeCell ref="BC15:BF15"/>
-    <mergeCell ref="BJ15:BL15"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="V21:X21"/>
     <mergeCell ref="Y21:AC21"/>
     <mergeCell ref="AD21:AG21"/>
     <mergeCell ref="AR14:AT14"/>
@@ -7934,15 +8005,23 @@
     <mergeCell ref="AX14:BB14"/>
     <mergeCell ref="BC14:BF14"/>
     <mergeCell ref="BG14:BI16"/>
-    <mergeCell ref="BJ14:BL14"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="BP14:BT14"/>
     <mergeCell ref="AR17:AT17"/>
     <mergeCell ref="Y18:AC18"/>
     <mergeCell ref="AD18:AG18"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="AW11:AZ11"/>
-    <mergeCell ref="BO11:BR11"/>
+    <mergeCell ref="Y19:AC19"/>
+    <mergeCell ref="AD19:AG19"/>
+    <mergeCell ref="AH19:AJ21"/>
+    <mergeCell ref="Y20:AC20"/>
+    <mergeCell ref="AD20:AG20"/>
+    <mergeCell ref="Y16:AC16"/>
+    <mergeCell ref="AD16:AG16"/>
+    <mergeCell ref="AH16:AJ18"/>
+    <mergeCell ref="Y17:AC17"/>
+    <mergeCell ref="AD17:AG17"/>
+    <mergeCell ref="AR19:AT19"/>
+    <mergeCell ref="AU19:AW19"/>
+    <mergeCell ref="AX19:BB19"/>
+    <mergeCell ref="BC19:BF19"/>
     <mergeCell ref="AR12:AT13"/>
     <mergeCell ref="AU12:AW12"/>
     <mergeCell ref="AX12:AY12"/>
@@ -7952,9 +8031,6 @@
     <mergeCell ref="BJ12:BL13"/>
     <mergeCell ref="BM12:BO12"/>
     <mergeCell ref="BP12:BQ12"/>
-    <mergeCell ref="Y19:AC19"/>
-    <mergeCell ref="AD19:AG19"/>
-    <mergeCell ref="AH19:AJ21"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="G20:K20"/>
@@ -7967,16 +8043,13 @@
     <mergeCell ref="L19:O19"/>
     <mergeCell ref="P19:R21"/>
     <mergeCell ref="S19:U19"/>
-    <mergeCell ref="Y20:AC20"/>
-    <mergeCell ref="AD20:AG20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="G21:K21"/>
     <mergeCell ref="L21:O21"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="Y16:AC16"/>
-    <mergeCell ref="AD16:AG16"/>
-    <mergeCell ref="AH16:AJ18"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="V19:X19"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="G17:K17"/>
@@ -7989,14 +8062,13 @@
     <mergeCell ref="L16:O16"/>
     <mergeCell ref="P16:R18"/>
     <mergeCell ref="S16:U16"/>
-    <mergeCell ref="Y17:AC17"/>
-    <mergeCell ref="AD17:AG17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="S18:U18"/>
     <mergeCell ref="V18:X18"/>
+    <mergeCell ref="V16:X16"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="L15:O15"/>
@@ -8238,8 +8310,6 @@
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="K32:O32"/>
     <mergeCell ref="BP27:BT27"/>
-    <mergeCell ref="AR23:AT24"/>
-    <mergeCell ref="AU23:AW23"/>
     <mergeCell ref="AX23:AY23"/>
     <mergeCell ref="BA23:BB23"/>
     <mergeCell ref="BP25:BT25"/>
@@ -8262,8 +8332,6 @@
     <mergeCell ref="BU9:CA9"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:I31"/>
-    <mergeCell ref="AW22:AZ22"/>
-    <mergeCell ref="BO22:BR22"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="K9:L9"/>
@@ -8283,6 +8351,8 @@
     <mergeCell ref="BU26:BX26"/>
     <mergeCell ref="BY28:CA30"/>
     <mergeCell ref="AD22:AG22"/>
+    <mergeCell ref="AR23:AT24"/>
+    <mergeCell ref="AU23:AW23"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="AR8:AY8"/>
     <mergeCell ref="AZ8:BF8"/>
@@ -8305,8 +8375,9 @@
     <mergeCell ref="BP5:BW5"/>
     <mergeCell ref="AV5:BE5"/>
     <mergeCell ref="BH4:BR4"/>
+    <mergeCell ref="BJ6:BM6"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -8327,28 +8398,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F29D37B3-0668-4912-99C0-F18CC5A8F08B}">
   <dimension ref="A1:AN70"/>
-  <sheetFormatPr defaultColWidth="8.33203125" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.35546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="4" width="2.33203125" customWidth="1"/>
+    <col min="1" max="4" width="2.35546875" customWidth="1"/>
     <col min="5" max="8" width="1" customWidth="1"/>
-    <col min="9" max="10" width="2.33203125" customWidth="1"/>
-    <col min="11" max="11" width="2.109375" customWidth="1"/>
+    <col min="9" max="10" width="2.35546875" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" customWidth="1"/>
     <col min="12" max="12" width="1" customWidth="1"/>
-    <col min="13" max="13" width="2.33203125" customWidth="1"/>
+    <col min="13" max="13" width="2.35546875" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="0.6640625" customWidth="1"/>
-    <col min="16" max="19" width="2.33203125" customWidth="1"/>
+    <col min="15" max="15" width="0.640625" customWidth="1"/>
+    <col min="16" max="19" width="2.35546875" customWidth="1"/>
     <col min="20" max="20" width="2" customWidth="1"/>
-    <col min="21" max="21" width="2.33203125" customWidth="1"/>
-    <col min="22" max="22" width="2.88671875" customWidth="1"/>
-    <col min="23" max="26" width="2.33203125" customWidth="1"/>
-    <col min="27" max="27" width="2.88671875" customWidth="1"/>
-    <col min="28" max="30" width="2.33203125" customWidth="1"/>
-    <col min="31" max="31" width="2.44140625" customWidth="1"/>
-    <col min="32" max="32" width="2.6640625" customWidth="1"/>
-    <col min="33" max="36" width="2.44140625" customWidth="1"/>
-    <col min="37" max="37" width="2.88671875" customWidth="1"/>
-    <col min="38" max="40" width="2.44140625" customWidth="1"/>
+    <col min="21" max="21" width="2.35546875" customWidth="1"/>
+    <col min="22" max="22" width="2.85546875" customWidth="1"/>
+    <col min="23" max="23" width="3.2109375" customWidth="1"/>
+    <col min="24" max="26" width="2.35546875" customWidth="1"/>
+    <col min="27" max="27" width="2.85546875" customWidth="1"/>
+    <col min="28" max="28" width="1.42578125" customWidth="1"/>
+    <col min="29" max="30" width="2.35546875" customWidth="1"/>
+    <col min="31" max="31" width="2.42578125" customWidth="1"/>
+    <col min="32" max="33" width="2.640625" customWidth="1"/>
+    <col min="34" max="36" width="2.42578125" customWidth="1"/>
+    <col min="37" max="37" width="2.85546875" customWidth="1"/>
+    <col min="38" max="38" width="2" customWidth="1"/>
+    <col min="39" max="40" width="2.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40">
@@ -8429,7 +8503,7 @@
       <c r="AN3" s="14"/>
     </row>
     <row r="4" spans="1:40">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="33" t="s">
         <v>171</v>
       </c>
       <c r="B4" s="13"/>
@@ -8446,21 +8520,21 @@
       <c r="M4" s="92"/>
       <c r="N4" s="92"/>
       <c r="O4" s="92"/>
-      <c r="P4" s="77" t="s">
+      <c r="P4" s="76" t="s">
         <v>208</v>
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
       <c r="AC4" s="13" t="s">
         <v>225</v>
       </c>
@@ -8491,18 +8565,18 @@
       <c r="L5" s="92"/>
       <c r="M5" s="92"/>
       <c r="N5" s="92"/>
-      <c r="O5" s="61" t="s">
+      <c r="O5" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="61"/>
-      <c r="V5" s="61"/>
-      <c r="W5" s="61"/>
-      <c r="X5" s="61"/>
+      <c r="P5" s="60"/>
+      <c r="Q5" s="60"/>
+      <c r="R5" s="60"/>
+      <c r="S5" s="60"/>
+      <c r="T5" s="60"/>
+      <c r="U5" s="60"/>
+      <c r="V5" s="60"/>
+      <c r="W5" s="60"/>
+      <c r="X5" s="60"/>
       <c r="Y5" s="92"/>
       <c r="Z5" s="92"/>
       <c r="AA5" s="92"/>
@@ -8522,8 +8596,8 @@
       <c r="AK5" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="AL5" s="33"/>
-      <c r="AM5" s="33"/>
+      <c r="AL5" s="32"/>
+      <c r="AM5" s="32"/>
       <c r="AN5" s="13"/>
     </row>
     <row r="6" spans="1:40">
@@ -8547,15 +8621,17 @@
       <c r="R6" s="91"/>
       <c r="S6" s="91"/>
       <c r="T6" s="91"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
+      <c r="U6" s="208" t="s">
+        <v>228</v>
+      </c>
+      <c r="V6" s="37"/>
+      <c r="W6" s="113"/>
+      <c r="X6" s="113"/>
+      <c r="Y6" s="113"/>
+      <c r="Z6" s="113"/>
+      <c r="AA6" s="21"/>
       <c r="AB6" s="19"/>
-      <c r="AC6" s="34"/>
+      <c r="AC6" s="33"/>
       <c r="AD6" s="13"/>
       <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
@@ -8565,49 +8641,49 @@
       <c r="AJ6" s="13"/>
       <c r="AK6" s="13"/>
       <c r="AL6" s="13"/>
-      <c r="AM6" s="62" t="s">
+      <c r="AM6" s="61" t="s">
         <v>210</v>
       </c>
       <c r="AN6" s="14"/>
     </row>
     <row r="7" spans="1:40" ht="15" customHeight="1">
       <c r="A7" s="135"/>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
       <c r="P7" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
-      <c r="S7" s="123"/>
+      <c r="Q7" s="122"/>
+      <c r="R7" s="122"/>
+      <c r="S7" s="122"/>
       <c r="T7" s="138"/>
       <c r="U7" s="137" t="s">
         <v>46</v>
       </c>
       <c r="V7" s="137"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="122" t="s">
+      <c r="W7" s="89"/>
+      <c r="X7" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="Y7" s="123"/>
+      <c r="Y7" s="122"/>
       <c r="Z7" s="139" t="s">
         <v>46</v>
       </c>
       <c r="AA7" s="137"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="122" t="s">
+      <c r="AB7" s="88"/>
+      <c r="AC7" s="121" t="s">
         <v>47</v>
       </c>
       <c r="AD7" s="138"/>
@@ -8709,7 +8785,7 @@
         <v>46</v>
       </c>
       <c r="AF9" s="126"/>
-      <c r="AG9" s="21"/>
+      <c r="AG9" s="89"/>
       <c r="AH9" s="127" t="s">
         <v>47</v>
       </c>
@@ -8718,14 +8794,14 @@
         <v>46</v>
       </c>
       <c r="AK9" s="126"/>
-      <c r="AL9" s="21"/>
+      <c r="AL9" s="88"/>
       <c r="AM9" s="127" t="s">
         <v>47</v>
       </c>
       <c r="AN9" s="128"/>
     </row>
     <row r="10" spans="1:40">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="55" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="7"/>
@@ -8733,11 +8809,11 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
       <c r="L10" s="18"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -8769,14 +8845,14 @@
       <c r="AN10" s="143"/>
     </row>
     <row r="11" spans="1:40">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
       <c r="L11" s="17"/>
       <c r="P11" s="142"/>
       <c r="Q11" s="143"/>
@@ -8804,15 +8880,15 @@
       <c r="AM11" s="143"/>
       <c r="AN11" s="143"/>
     </row>
-    <row r="12" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A12" s="57" t="s">
+    <row r="12" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A12" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
       <c r="L12" s="17"/>
       <c r="P12" s="142"/>
       <c r="Q12" s="143"/>
@@ -8840,15 +8916,15 @@
       <c r="AM12" s="143"/>
       <c r="AN12" s="143"/>
     </row>
-    <row r="13" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A13" s="57" t="s">
+    <row r="13" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A13" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="17"/>
       <c r="P13" s="142"/>
       <c r="Q13" s="143"/>
@@ -8876,15 +8952,15 @@
       <c r="AM13" s="143"/>
       <c r="AN13" s="143"/>
     </row>
-    <row r="14" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A14" s="57" t="s">
+    <row r="14" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A14" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
       <c r="L14" s="17"/>
       <c r="P14" s="142"/>
       <c r="Q14" s="143"/>
@@ -8912,15 +8988,15 @@
       <c r="AM14" s="143"/>
       <c r="AN14" s="143"/>
     </row>
-    <row r="15" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A15" s="57" t="s">
+    <row r="15" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A15" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
       <c r="L15" s="17"/>
       <c r="P15" s="142"/>
       <c r="Q15" s="143"/>
@@ -8948,15 +9024,15 @@
       <c r="AM15" s="143"/>
       <c r="AN15" s="143"/>
     </row>
-    <row r="16" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A16" s="57" t="s">
+    <row r="16" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A16" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
       <c r="L16" s="17"/>
       <c r="P16" s="142"/>
       <c r="Q16" s="143"/>
@@ -8984,15 +9060,15 @@
       <c r="AM16" s="143"/>
       <c r="AN16" s="143"/>
     </row>
-    <row r="17" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A17" s="57" t="s">
+    <row r="17" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A17" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
       <c r="L17" s="17"/>
       <c r="P17" s="142"/>
       <c r="Q17" s="143"/>
@@ -9020,15 +9096,15 @@
       <c r="AM17" s="143"/>
       <c r="AN17" s="143"/>
     </row>
-    <row r="18" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A18" s="57" t="s">
+    <row r="18" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A18" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
       <c r="L18" s="17"/>
       <c r="P18" s="142"/>
       <c r="Q18" s="143"/>
@@ -9056,15 +9132,15 @@
       <c r="AM18" s="143"/>
       <c r="AN18" s="143"/>
     </row>
-    <row r="19" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A19" s="57" t="s">
+    <row r="19" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A19" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
       <c r="L19" s="17"/>
       <c r="P19" s="142"/>
       <c r="Q19" s="143"/>
@@ -9092,15 +9168,15 @@
       <c r="AM19" s="143"/>
       <c r="AN19" s="143"/>
     </row>
-    <row r="20" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A20" s="57" t="s">
+    <row r="20" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A20" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
       <c r="L20" s="17"/>
       <c r="P20" s="142"/>
       <c r="Q20" s="143"/>
@@ -9128,15 +9204,15 @@
       <c r="AM20" s="143"/>
       <c r="AN20" s="143"/>
     </row>
-    <row r="21" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A21" s="57" t="s">
+    <row r="21" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A21" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
       <c r="L21" s="17"/>
       <c r="P21" s="142"/>
       <c r="Q21" s="143"/>
@@ -9164,15 +9240,15 @@
       <c r="AM21" s="143"/>
       <c r="AN21" s="143"/>
     </row>
-    <row r="22" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A22" s="58" t="s">
+    <row r="22" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A22" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
       <c r="L22" s="17"/>
       <c r="P22" s="142"/>
       <c r="Q22" s="143"/>
@@ -9200,15 +9276,15 @@
       <c r="AM22" s="143"/>
       <c r="AN22" s="143"/>
     </row>
-    <row r="23" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A23" s="57" t="s">
+    <row r="23" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A23" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
       <c r="L23" s="17"/>
       <c r="P23" s="142"/>
       <c r="Q23" s="143"/>
@@ -9236,15 +9312,15 @@
       <c r="AM23" s="143"/>
       <c r="AN23" s="143"/>
     </row>
-    <row r="24" spans="1:40" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="A24" s="64" t="s">
+    <row r="24" spans="1:40" ht="18.649999999999999" customHeight="1" thickBot="1">
+      <c r="A24" s="63" t="s">
         <v>177</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
       <c r="L24" s="17"/>
       <c r="P24" s="144"/>
       <c r="Q24" s="145"/>
@@ -9272,24 +9348,24 @@
       <c r="AM24" s="145"/>
       <c r="AN24" s="145"/>
     </row>
-    <row r="25" spans="1:40" ht="18.600000000000001" customHeight="1" thickTop="1">
-      <c r="A25" s="57" t="s">
+    <row r="25" spans="1:40" ht="18.649999999999999" customHeight="1" thickTop="1">
+      <c r="A25" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
       <c r="P25" s="146"/>
       <c r="Q25" s="147"/>
       <c r="R25" s="147"/>
@@ -9316,15 +9392,15 @@
       <c r="AM25" s="147"/>
       <c r="AN25" s="147"/>
     </row>
-    <row r="26" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A26" s="57" t="s">
+    <row r="26" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A26" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
       <c r="L26" s="17"/>
       <c r="P26" s="142"/>
       <c r="Q26" s="143"/>
@@ -9352,15 +9428,15 @@
       <c r="AM26" s="143"/>
       <c r="AN26" s="143"/>
     </row>
-    <row r="27" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A27" s="57" t="s">
+    <row r="27" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A27" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
       <c r="L27" s="17"/>
       <c r="P27" s="142"/>
       <c r="Q27" s="143"/>
@@ -9388,15 +9464,15 @@
       <c r="AM27" s="143"/>
       <c r="AN27" s="143"/>
     </row>
-    <row r="28" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A28" s="57" t="s">
+    <row r="28" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A28" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
       <c r="L28" s="17"/>
       <c r="P28" s="142"/>
       <c r="Q28" s="143"/>
@@ -9424,15 +9500,15 @@
       <c r="AM28" s="143"/>
       <c r="AN28" s="143"/>
     </row>
-    <row r="29" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A29" s="57" t="s">
+    <row r="29" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A29" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
       <c r="L29" s="17"/>
       <c r="P29" s="142"/>
       <c r="Q29" s="143"/>
@@ -9460,15 +9536,15 @@
       <c r="AM29" s="143"/>
       <c r="AN29" s="143"/>
     </row>
-    <row r="30" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A30" s="57" t="s">
+    <row r="30" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A30" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
       <c r="L30" s="17"/>
       <c r="P30" s="142"/>
       <c r="Q30" s="143"/>
@@ -9496,15 +9572,15 @@
       <c r="AM30" s="143"/>
       <c r="AN30" s="143"/>
     </row>
-    <row r="31" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A31" s="57" t="s">
+    <row r="31" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A31" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
       <c r="L31" s="17"/>
       <c r="P31" s="142"/>
       <c r="Q31" s="143"/>
@@ -9532,15 +9608,15 @@
       <c r="AM31" s="143"/>
       <c r="AN31" s="143"/>
     </row>
-    <row r="32" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A32" s="57" t="s">
+    <row r="32" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A32" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
       <c r="L32" s="17"/>
       <c r="P32" s="142"/>
       <c r="Q32" s="143"/>
@@ -9568,15 +9644,15 @@
       <c r="AM32" s="143"/>
       <c r="AN32" s="143"/>
     </row>
-    <row r="33" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A33" s="57" t="s">
+    <row r="33" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A33" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
       <c r="L33" s="17"/>
       <c r="P33" s="142"/>
       <c r="Q33" s="143"/>
@@ -9604,8 +9680,8 @@
       <c r="AM33" s="143"/>
       <c r="AN33" s="143"/>
     </row>
-    <row r="34" spans="1:40" ht="18.600000000000001" customHeight="1">
-      <c r="A34" s="59" t="s">
+    <row r="34" spans="1:40" ht="18.649999999999999" customHeight="1">
+      <c r="A34" s="58" t="s">
         <v>69</v>
       </c>
       <c r="B34" s="9"/>
@@ -9743,7 +9819,7 @@
     <row r="69" ht="15" customHeight="1"/>
     <row r="70" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="143">
+  <mergeCells count="144">
     <mergeCell ref="P33:T33"/>
     <mergeCell ref="U33:Y33"/>
     <mergeCell ref="Z33:AD33"/>
@@ -9887,8 +9963,9 @@
     <mergeCell ref="AE7:AI8"/>
     <mergeCell ref="AJ7:AN8"/>
     <mergeCell ref="S4:AB4"/>
+    <mergeCell ref="W6:Z6"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -9909,17 +9986,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="4.44140625" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" customWidth="1"/>
-    <col min="6" max="7" width="4.6640625" customWidth="1"/>
-    <col min="8" max="11" width="2.33203125" customWidth="1"/>
-    <col min="12" max="17" width="4.6640625" customWidth="1"/>
-    <col min="18" max="18" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.35546875" customWidth="1"/>
+    <col min="4" max="4" width="4.42578125" customWidth="1"/>
+    <col min="5" max="5" width="5.35546875" customWidth="1"/>
+    <col min="6" max="7" width="4.640625" customWidth="1"/>
+    <col min="8" max="11" width="2.35546875" customWidth="1"/>
+    <col min="12" max="17" width="4.640625" customWidth="1"/>
+    <col min="18" max="18" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -9944,7 +10021,7 @@
       <c r="Q1" s="163"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="15.6">
+    <row r="2" spans="1:18" ht="15">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -9986,14 +10063,14 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="27"/>
+      <c r="B4" s="26"/>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="66"/>
+      <c r="E4" s="65"/>
       <c r="F4" t="s">
         <v>79</v>
       </c>
@@ -10007,28 +10084,28 @@
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="30"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="31" t="s">
+      <c r="J5" s="31"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="N5" s="31"/>
+      <c r="N5" s="30"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -10040,13 +10117,13 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="30"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="31"/>
+      <c r="M6" s="30"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -10064,8 +10141,8 @@
       <c r="F7" s="157"/>
       <c r="G7" s="158"/>
       <c r="H7" s="157"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="114"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
       <c r="K7" s="158"/>
       <c r="L7" s="157"/>
       <c r="M7" s="158"/>
@@ -10086,8 +10163,8 @@
       <c r="F8" s="148"/>
       <c r="G8" s="149"/>
       <c r="H8" s="157"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="115"/>
       <c r="K8" s="158"/>
       <c r="L8" s="148"/>
       <c r="M8" s="149"/>
@@ -10108,8 +10185,8 @@
       <c r="F9" s="148"/>
       <c r="G9" s="149"/>
       <c r="H9" s="157"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="114"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
       <c r="K9" s="158"/>
       <c r="L9" s="148"/>
       <c r="M9" s="149"/>
@@ -10130,8 +10207,8 @@
       <c r="F10" s="148"/>
       <c r="G10" s="149"/>
       <c r="H10" s="157"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="114"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
       <c r="K10" s="158"/>
       <c r="L10" s="148"/>
       <c r="M10" s="149"/>
@@ -10152,8 +10229,8 @@
       <c r="F11" s="148"/>
       <c r="G11" s="149"/>
       <c r="H11" s="157"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="114"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
       <c r="K11" s="158"/>
       <c r="L11" s="148"/>
       <c r="M11" s="149"/>
@@ -10174,8 +10251,8 @@
       <c r="F12" s="148"/>
       <c r="G12" s="149"/>
       <c r="H12" s="157"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="114"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="115"/>
       <c r="K12" s="158"/>
       <c r="L12" s="148"/>
       <c r="M12" s="149"/>
@@ -10196,8 +10273,8 @@
       <c r="F13" s="148"/>
       <c r="G13" s="149"/>
       <c r="H13" s="157"/>
-      <c r="I13" s="114"/>
-      <c r="J13" s="114"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
       <c r="K13" s="158"/>
       <c r="L13" s="148"/>
       <c r="M13" s="149"/>
@@ -10218,8 +10295,8 @@
       <c r="F14" s="148"/>
       <c r="G14" s="149"/>
       <c r="H14" s="157"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="114"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="115"/>
       <c r="K14" s="158"/>
       <c r="L14" s="148"/>
       <c r="M14" s="149"/>
@@ -10240,8 +10317,8 @@
       <c r="F15" s="148"/>
       <c r="G15" s="149"/>
       <c r="H15" s="157"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
       <c r="K15" s="158"/>
       <c r="L15" s="148"/>
       <c r="M15" s="149"/>
@@ -10313,7 +10390,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" ht="15.6">
+    <row r="19" spans="1:18" ht="15">
       <c r="A19" s="5" t="s">
         <v>12</v>
       </c>
@@ -10366,8 +10443,8 @@
       <c r="F21" s="156"/>
       <c r="G21" s="156"/>
       <c r="H21" s="157"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="115"/>
       <c r="K21" s="158"/>
       <c r="L21" s="156"/>
       <c r="M21" s="156"/>
@@ -10459,7 +10536,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="27" spans="1:18" ht="15.6">
+    <row r="27" spans="1:18" ht="15">
       <c r="A27" s="5" t="s">
         <v>15</v>
       </c>
@@ -10470,27 +10547,27 @@
       <c r="C28" s="91"/>
       <c r="D28" s="91"/>
     </row>
-    <row r="29" spans="1:18" ht="14.4">
-      <c r="A29" s="31" t="s">
+    <row r="29" spans="1:18" ht="14.6">
+      <c r="A29" s="30" t="s">
         <v>173</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="50"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B30" s="7"/>
-      <c r="C30" s="86"/>
+      <c r="C30" s="84"/>
       <c r="D30" s="156"/>
       <c r="E30" s="156"/>
       <c r="F30" s="156"/>
       <c r="G30" s="156"/>
       <c r="H30" s="157"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="115"/>
       <c r="K30" s="158"/>
       <c r="L30" s="156"/>
       <c r="M30" s="156"/>
@@ -10503,8 +10580,8 @@
       <c r="A31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="60"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="143"/>
       <c r="E31" s="143"/>
       <c r="F31" s="143"/>
@@ -10525,7 +10602,7 @@
         <v>18</v>
       </c>
       <c r="B32" s="9"/>
-      <c r="C32" s="60"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="143"/>
       <c r="E32" s="143"/>
       <c r="F32" s="143"/>
@@ -10659,7 +10736,7 @@
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="N10:O10"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -10678,9 +10755,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O36"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="4" max="15" width="4.88671875" customWidth="1"/>
+    <col min="4" max="15" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -10702,7 +10779,7 @@
       <c r="N1" s="163"/>
       <c r="O1" s="163"/>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
+    <row r="2" spans="1:15" ht="15">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -10721,7 +10798,7 @@
         <v>20</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -11038,7 +11115,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.6">
+    <row r="24" spans="1:15" ht="15">
       <c r="A24" s="2" t="s">
         <v>184</v>
       </c>
@@ -11052,7 +11129,7 @@
       <c r="F25" s="91"/>
       <c r="G25" s="91"/>
       <c r="K25" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -11212,8 +11289,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15.6">
-      <c r="A36" s="70"/>
+    <row r="36" spans="1:15" ht="15">
+      <c r="A36" s="69"/>
       <c r="H36" s="15"/>
     </row>
   </sheetData>
@@ -11390,7 +11467,7 @@
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="A3:G3"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -11408,9 +11485,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E25DF9-4B2C-48B4-B27D-459DA0F7DA9F}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.15"/>
   <cols>
-    <col min="4" max="15" width="4.88671875" customWidth="1"/>
+    <col min="4" max="15" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -11432,29 +11509,29 @@
       <c r="N1" s="163"/>
       <c r="O1" s="163"/>
     </row>
-    <row r="2" spans="1:15" ht="15.6">
-      <c r="A2" s="70" t="s">
+    <row r="2" spans="1:15" ht="15">
+      <c r="A2" s="69" t="s">
         <v>185</v>
       </c>
       <c r="H2" s="15"/>
     </row>
-    <row r="3" spans="1:15" ht="13.8" customHeight="1">
+    <row r="3" spans="1:15" ht="13.85" customHeight="1">
       <c r="A3" s="91"/>
       <c r="B3" s="91"/>
       <c r="C3" s="91"/>
       <c r="D3" s="91"/>
       <c r="E3" s="15"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="33" t="s">
+      <c r="G3" s="87"/>
+      <c r="H3" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="88" t="s">
+      <c r="I3" s="86"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="86" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="13.8" customHeight="1">
+    <row r="4" spans="1:15" ht="13.85" customHeight="1">
       <c r="A4" s="187" t="s">
         <v>194</v>
       </c>
@@ -11473,7 +11550,7 @@
       <c r="N4" s="157"/>
       <c r="O4" s="158"/>
     </row>
-    <row r="5" spans="1:15" ht="13.8" customHeight="1">
+    <row r="5" spans="1:15" ht="13.85" customHeight="1">
       <c r="A5" s="188" t="s">
         <v>186</v>
       </c>
@@ -11492,7 +11569,7 @@
       <c r="N5" s="148"/>
       <c r="O5" s="149"/>
     </row>
-    <row r="6" spans="1:15" ht="13.8" customHeight="1">
+    <row r="6" spans="1:15" ht="13.85" customHeight="1">
       <c r="A6" s="180" t="s">
         <v>189</v>
       </c>
@@ -11511,7 +11588,7 @@
       <c r="N6" s="171"/>
       <c r="O6" s="172"/>
     </row>
-    <row r="7" spans="1:15" ht="13.8" customHeight="1">
+    <row r="7" spans="1:15" ht="13.85" customHeight="1">
       <c r="A7" s="183"/>
       <c r="B7" s="184"/>
       <c r="C7" s="185"/>
@@ -11528,7 +11605,7 @@
       <c r="N7" s="173"/>
       <c r="O7" s="174"/>
     </row>
-    <row r="8" spans="1:15" ht="13.8" customHeight="1">
+    <row r="8" spans="1:15" ht="13.85" customHeight="1">
       <c r="A8" s="175" t="s">
         <v>188</v>
       </c>
@@ -11547,7 +11624,7 @@
       <c r="N8" s="175"/>
       <c r="O8" s="176"/>
     </row>
-    <row r="9" spans="1:15" ht="13.8" customHeight="1">
+    <row r="9" spans="1:15" ht="13.85" customHeight="1">
       <c r="A9" s="177" t="s">
         <v>187</v>
       </c>
@@ -11566,7 +11643,7 @@
       <c r="N9" s="148"/>
       <c r="O9" s="149"/>
     </row>
-    <row r="10" spans="1:15" ht="13.8" customHeight="1">
+    <row r="10" spans="1:15" ht="13.85" customHeight="1">
       <c r="A10" s="180" t="s">
         <v>189</v>
       </c>
@@ -11585,7 +11662,7 @@
       <c r="N10" s="171"/>
       <c r="O10" s="172"/>
     </row>
-    <row r="11" spans="1:15" ht="13.8" customHeight="1">
+    <row r="11" spans="1:15" ht="13.85" customHeight="1">
       <c r="A11" s="183"/>
       <c r="B11" s="184"/>
       <c r="C11" s="185"/>
@@ -11602,7 +11679,7 @@
       <c r="N11" s="173"/>
       <c r="O11" s="174"/>
     </row>
-    <row r="12" spans="1:15" ht="13.8" customHeight="1">
+    <row r="12" spans="1:15" ht="13.85" customHeight="1">
       <c r="A12" s="175" t="s">
         <v>188</v>
       </c>
@@ -11622,7 +11699,7 @@
       <c r="O12" s="176"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="30" t="s">
         <v>193</v>
       </c>
       <c r="J13" s="11" t="s">
@@ -11630,7 +11707,7 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="53" t="s">
         <v>190</v>
       </c>
       <c r="B14" t="s">
@@ -11648,142 +11725,142 @@
       <c r="L15" s="92"/>
       <c r="M15" s="92"/>
     </row>
-    <row r="17" spans="1:10" ht="15.6">
-      <c r="A17" s="70" t="s">
+    <row r="17" spans="1:10" ht="15">
+      <c r="A17" s="69" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="68" t="s">
         <v>181</v>
       </c>
       <c r="B18" s="92"/>
       <c r="C18" s="92"/>
     </row>
-    <row r="19" spans="1:10" ht="14.4">
-      <c r="A19" s="69" t="s">
+    <row r="19" spans="1:10">
+      <c r="A19" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="71" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="J20" s="71"/>
+      <c r="J20" s="70"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="F21" s="73" t="s">
+      <c r="F21" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="J21" s="71"/>
+      <c r="J21" s="70"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="F22" s="73" t="s">
+      <c r="F22" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="J22" s="71"/>
+      <c r="J22" s="70"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="69" t="s">
+      <c r="A24" s="68" t="s">
         <v>181</v>
       </c>
       <c r="B24" s="92"/>
       <c r="C24" s="92"/>
     </row>
-    <row r="25" spans="1:10" ht="14.4">
-      <c r="A25" s="69" t="s">
+    <row r="25" spans="1:10">
+      <c r="A25" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="F25" s="72" t="s">
+      <c r="F25" s="71" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="F26" s="73" t="s">
+      <c r="F26" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="J26" s="71"/>
+      <c r="J26" s="70"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="F27" s="73" t="s">
+      <c r="F27" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="J27" s="71"/>
+      <c r="J27" s="70"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="F28" s="73" t="s">
+      <c r="F28" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="J28" s="71"/>
+      <c r="J28" s="70"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="69" t="s">
+      <c r="A30" s="68" t="s">
         <v>181</v>
       </c>
       <c r="B30" s="92"/>
       <c r="C30" s="92"/>
     </row>
-    <row r="31" spans="1:10" ht="14.4">
-      <c r="A31" s="69" t="s">
+    <row r="31" spans="1:10">
+      <c r="A31" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="F31" s="72" t="s">
+      <c r="F31" s="71" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="F32" s="73" t="s">
+      <c r="F32" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="J32" s="71"/>
+      <c r="J32" s="70"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="J33" s="71"/>
+      <c r="J33" s="70"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="J34" s="71"/>
+      <c r="J34" s="70"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="69" t="s">
+      <c r="A36" s="68" t="s">
         <v>181</v>
       </c>
       <c r="B36" s="92"/>
       <c r="C36" s="92"/>
     </row>
-    <row r="37" spans="1:10" ht="14.4">
-      <c r="A37" s="69" t="s">
+    <row r="37" spans="1:10">
+      <c r="A37" s="68" t="s">
         <v>195</v>
       </c>
-      <c r="F37" s="72" t="s">
+      <c r="F37" s="71" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="F38" s="73" t="s">
+      <c r="F38" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="J38" s="71"/>
+      <c r="J38" s="70"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="F39" s="73" t="s">
+      <c r="F39" s="72" t="s">
         <v>198</v>
       </c>
-      <c r="J39" s="71"/>
+      <c r="J39" s="70"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="F40" s="73" t="s">
+      <c r="F40" s="72" t="s">
         <v>199</v>
       </c>
-      <c r="J40" s="71"/>
+      <c r="J40" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="44">
@@ -11832,7 +11909,7 @@
     <mergeCell ref="A10:C11"/>
     <mergeCell ref="A12:C12"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -11850,11 +11927,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2675AEB6-CFB2-4A66-B05D-DEA568A2BBC1}">
   <dimension ref="A1:V39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="21" width="3.88671875" customWidth="1"/>
-    <col min="22" max="22" width="4.33203125" customWidth="1"/>
+    <col min="1" max="3" width="4.35546875" customWidth="1"/>
+    <col min="4" max="21" width="3.85546875" customWidth="1"/>
+    <col min="22" max="22" width="4.35546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -11883,7 +11960,7 @@
       <c r="U1" s="191"/>
       <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="15.6">
+    <row r="2" spans="1:22" ht="15">
       <c r="A2" s="5" t="s">
         <v>202</v>
       </c>
@@ -11899,12 +11976,12 @@
       <c r="V3" s="1"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="67" t="s">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="66" t="s">
         <v>175</v>
       </c>
       <c r="G4" s="92"/>
@@ -11924,19 +12001,19 @@
       <c r="E5" s="151"/>
       <c r="F5" s="152"/>
       <c r="G5" s="157"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
       <c r="J5" s="157"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
       <c r="M5" s="157"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="114"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
       <c r="P5" s="157"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="114"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="115"/>
       <c r="S5" s="157"/>
-      <c r="T5" s="114"/>
+      <c r="T5" s="115"/>
       <c r="U5" s="158"/>
       <c r="V5" s="1"/>
     </row>
@@ -11950,45 +12027,45 @@
       <c r="E6" s="206"/>
       <c r="F6" s="206"/>
       <c r="G6" s="157"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="114"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
       <c r="J6" s="157"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
       <c r="M6" s="157"/>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
       <c r="P6" s="157"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="114"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115"/>
       <c r="S6" s="157"/>
-      <c r="T6" s="114"/>
+      <c r="T6" s="115"/>
       <c r="U6" s="158"/>
       <c r="V6" s="1"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
       <c r="D7" s="194"/>
       <c r="E7" s="194"/>
       <c r="F7" s="194"/>
       <c r="G7" s="157"/>
-      <c r="H7" s="114"/>
-      <c r="I7" s="114"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
       <c r="J7" s="157"/>
-      <c r="K7" s="114"/>
-      <c r="L7" s="114"/>
+      <c r="K7" s="115"/>
+      <c r="L7" s="115"/>
       <c r="M7" s="157"/>
-      <c r="N7" s="114"/>
-      <c r="O7" s="114"/>
+      <c r="N7" s="115"/>
+      <c r="O7" s="115"/>
       <c r="P7" s="157"/>
-      <c r="Q7" s="114"/>
-      <c r="R7" s="114"/>
+      <c r="Q7" s="115"/>
+      <c r="R7" s="115"/>
       <c r="S7" s="157"/>
-      <c r="T7" s="114"/>
+      <c r="T7" s="115"/>
       <c r="U7" s="158"/>
       <c r="V7" s="1"/>
     </row>
@@ -12002,19 +12079,19 @@
       <c r="E8" s="194"/>
       <c r="F8" s="194"/>
       <c r="G8" s="157"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="114"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
       <c r="J8" s="157"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="115"/>
       <c r="M8" s="157"/>
-      <c r="N8" s="114"/>
-      <c r="O8" s="114"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="115"/>
       <c r="P8" s="157"/>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="114"/>
+      <c r="Q8" s="115"/>
+      <c r="R8" s="115"/>
       <c r="S8" s="157"/>
-      <c r="T8" s="114"/>
+      <c r="T8" s="115"/>
       <c r="U8" s="158"/>
       <c r="V8" s="1"/>
     </row>
@@ -12027,30 +12104,30 @@
     <row r="10" spans="1:22">
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:22" ht="15.6">
-      <c r="A11" s="47" t="s">
+    <row r="11" spans="1:22" ht="15">
+      <c r="A11" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="33"/>
       <c r="V11" s="1"/>
     </row>
     <row r="12" spans="1:22">
@@ -12063,46 +12140,46 @@
       <c r="G12" s="94"/>
       <c r="H12" s="94"/>
       <c r="I12" s="94"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="15.6">
-      <c r="A13" s="74" t="s">
+    <row r="13" spans="1:22" ht="15">
+      <c r="A13" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
       <c r="G13" s="195"/>
       <c r="H13" s="195"/>
       <c r="I13" s="195"/>
-      <c r="J13" s="34" t="s">
+      <c r="J13" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="K13" s="34"/>
+      <c r="K13" s="33"/>
       <c r="L13" s="110"/>
       <c r="M13" s="110"/>
       <c r="N13" s="110"/>
       <c r="O13" s="110"/>
       <c r="P13" s="110"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="33"/>
       <c r="V13" s="1"/>
     </row>
     <row r="14" spans="1:22">
@@ -12116,17 +12193,17 @@
       <c r="H14" s="196"/>
       <c r="I14" s="196"/>
       <c r="J14" s="196"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
       <c r="V14" s="1"/>
     </row>
     <row r="15" spans="1:22">
@@ -12358,33 +12435,33 @@
       <c r="U22" s="143"/>
     </row>
     <row r="23" spans="1:22">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="33"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="26" spans="1:22" ht="15.6">
-      <c r="A26" s="47" t="s">
+    <row r="26" spans="1:22" ht="15">
+      <c r="A26" s="46" t="s">
         <v>206</v>
       </c>
     </row>
@@ -12400,12 +12477,12 @@
       <c r="I27" s="94"/>
     </row>
     <row r="28" spans="1:22">
-      <c r="A28" s="46" t="s">
+      <c r="A28" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
       <c r="H28" s="11" t="s">
         <v>214</v>
       </c>
@@ -12461,7 +12538,7 @@
       <c r="U31" s="143"/>
     </row>
     <row r="32" spans="1:22">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="45" t="s">
         <v>11</v>
       </c>
     </row>
@@ -12595,7 +12672,7 @@
     <mergeCell ref="M8:O8"/>
     <mergeCell ref="J5:L5"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.82677165354330695" bottom="0.98425196850393704" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
